--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,6 +1345,3499 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132519362</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411626</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6705988</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132519415</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411923</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706141</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132519427</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79074</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411777</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6706085</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132514331</v>
+      </c>
+      <c r="B11" t="n">
+        <v>81302</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sörsjön Väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411764</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6706079</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132519436</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>353</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>411770</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6706091</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132519431</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>411628</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6705976</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132519365</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>411760</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6706093</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132519422</v>
+      </c>
+      <c r="B15" t="n">
+        <v>81302</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>411724</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6706038</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132519433</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>411844</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6706175</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132519403</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>411785</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6706078</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132519396</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>411744</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6706031</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132519367</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>411782</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6706088</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132519428</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79074</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>411921</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6706127</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132519372</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>411724</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6706038</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132519424</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79074</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>411626</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6705984</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132514329</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sörsjön Väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>411914</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6706129</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132519400</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>411772</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6706097</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132519398</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>411777</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6706088</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132519418</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>411942</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6706165</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132519392</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>411724</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6706039</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132519430</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>411592</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6705990</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132519435</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78983</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>353</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>411612</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6705977</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132519390</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>411626</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6705987</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132519394</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>411741</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6706031</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132519376</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79403</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>411939</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6706156</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132519413</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>411921</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6706127</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132514333</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sörsjön Väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>411597</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6705968</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132514332</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79074</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sörsjön Väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6706124</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132519408</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>411867</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6706121</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132519364</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>411743</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6706033</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132519432</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>411775</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6706079</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132519405</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>411830</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6706163</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132519388</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>411615</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6705973</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132519374</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>411937</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6706170</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132519370</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>411829</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6706165</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132519411</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>H, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>411909</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6706115</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132519362</v>
+        <v>132514331</v>
       </c>
       <c r="B8" t="n">
-        <v>79936</v>
+        <v>81302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,37 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411626</v>
+        <v>411764</v>
       </c>
       <c r="R8" t="n">
-        <v>6705988</v>
+        <v>6706079</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132519415</v>
+        <v>132519362</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411923</v>
+        <v>411626</v>
       </c>
       <c r="R9" t="n">
-        <v>6706141</v>
+        <v>6705988</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132519427</v>
+        <v>132519415</v>
       </c>
       <c r="B10" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411777</v>
+        <v>411923</v>
       </c>
       <c r="R10" t="n">
-        <v>6706085</v>
+        <v>6706141</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132514331</v>
+        <v>132519427</v>
       </c>
       <c r="B11" t="n">
-        <v>81302</v>
+        <v>79074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,37 +1649,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411764</v>
+        <v>411777</v>
       </c>
       <c r="R11" t="n">
-        <v>6706079</v>
+        <v>6706085</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,12 +1723,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4838,6 +4838,1461 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132640387</v>
+      </c>
+      <c r="B44" t="n">
+        <v>81302</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>411499</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6705949</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132640080</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>411577</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6705969</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132640284</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>411522</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6705950</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132640439</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>411503</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6705939</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132640452</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>411494</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6705946</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132639607</v>
+      </c>
+      <c r="B49" t="n">
+        <v>83289</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>308</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>411648</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6705948</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132639955</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>411559</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6705948</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132640069</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>411560</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6705975</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132640306</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>411517</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6705932</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132639985</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>411571</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6705940</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132639564</v>
+      </c>
+      <c r="B54" t="n">
+        <v>83289</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>308</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>411663</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6705970</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132640187</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>411549</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6705962</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132640049</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>411557</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6705961</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132641415</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>411518</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6705877</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132640952</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>411454</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6705886</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132514331</v>
+        <v>132519362</v>
       </c>
       <c r="B8" t="n">
-        <v>81302</v>
+        <v>79938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,37 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411764</v>
+        <v>411626</v>
       </c>
       <c r="R8" t="n">
-        <v>6706079</v>
+        <v>6705988</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132519362</v>
+        <v>132519427</v>
       </c>
       <c r="B9" t="n">
-        <v>79936</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411626</v>
+        <v>411777</v>
       </c>
       <c r="R9" t="n">
-        <v>6705988</v>
+        <v>6706085</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132519415</v>
+        <v>132514331</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>81304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,37 +1552,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411923</v>
+        <v>411764</v>
       </c>
       <c r="R10" t="n">
-        <v>6706141</v>
+        <v>6706079</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132519427</v>
+        <v>132519415</v>
       </c>
       <c r="B11" t="n">
-        <v>79074</v>
+        <v>79077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411777</v>
+        <v>411923</v>
       </c>
       <c r="R11" t="n">
-        <v>6706085</v>
+        <v>6706141</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1738,7 +1738,7 @@
         <v>132519436</v>
       </c>
       <c r="B12" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>132519431</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>132519365</v>
       </c>
       <c r="B14" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132519422</v>
       </c>
       <c r="B15" t="n">
-        <v>81302</v>
+        <v>81304</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>132519433</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132519403</v>
+        <v>132519367</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79938</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,21 +2232,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411785</v>
+        <v>411782</v>
       </c>
       <c r="R17" t="n">
-        <v>6706078</v>
+        <v>6706088</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2321,7 +2321,7 @@
         <v>132519396</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132519367</v>
+        <v>132519403</v>
       </c>
       <c r="B19" t="n">
-        <v>79936</v>
+        <v>79077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411782</v>
+        <v>411785</v>
       </c>
       <c r="R19" t="n">
-        <v>6706088</v>
+        <v>6706078</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
         <v>132519428</v>
       </c>
       <c r="B20" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132519372</v>
+        <v>132519424</v>
       </c>
       <c r="B21" t="n">
-        <v>79936</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>411724</v>
+        <v>411626</v>
       </c>
       <c r="R21" t="n">
-        <v>6706038</v>
+        <v>6705984</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132519424</v>
+        <v>132519372</v>
       </c>
       <c r="B22" t="n">
-        <v>79074</v>
+        <v>79938</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411626</v>
+        <v>411724</v>
       </c>
       <c r="R22" t="n">
-        <v>6705984</v>
+        <v>6706038</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         <v>132514329</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>132519400</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2997,10 +2997,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132519398</v>
+        <v>132519418</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411777</v>
+        <v>411942</v>
       </c>
       <c r="R25" t="n">
-        <v>6706088</v>
+        <v>6706165</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3094,10 +3094,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132519418</v>
+        <v>132519392</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>411942</v>
+        <v>411724</v>
       </c>
       <c r="R26" t="n">
-        <v>6706165</v>
+        <v>6706039</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3191,10 +3191,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132519392</v>
+        <v>132519398</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411724</v>
+        <v>411777</v>
       </c>
       <c r="R27" t="n">
-        <v>6706039</v>
+        <v>6706088</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>132519430</v>
       </c>
       <c r="B28" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>132519435</v>
       </c>
       <c r="B29" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>132519390</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>132519394</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3676,32 +3676,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132519376</v>
+        <v>132519413</v>
       </c>
       <c r="B32" t="n">
-        <v>79403</v>
+        <v>79077</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411939</v>
+        <v>411921</v>
       </c>
       <c r="R32" t="n">
-        <v>6706156</v>
+        <v>6706127</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3773,32 +3773,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132519413</v>
+        <v>132519376</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411921</v>
+        <v>411939</v>
       </c>
       <c r="R33" t="n">
-        <v>6706127</v>
+        <v>6706156</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132514333</v>
+        <v>132514332</v>
       </c>
       <c r="B34" t="n">
-        <v>79317</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411597</v>
+        <v>411910</v>
       </c>
       <c r="R34" t="n">
-        <v>6705968</v>
+        <v>6706124</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132514332</v>
+        <v>132519364</v>
       </c>
       <c r="B35" t="n">
-        <v>79074</v>
+        <v>79938</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,37 +3978,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411910</v>
+        <v>411743</v>
       </c>
       <c r="R35" t="n">
-        <v>6706124</v>
+        <v>6706033</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4052,22 +4052,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132519408</v>
+        <v>132514333</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>79319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,37 +4075,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411867</v>
+        <v>411597</v>
       </c>
       <c r="R36" t="n">
-        <v>6706121</v>
+        <v>6705968</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132519364</v>
+        <v>132519432</v>
       </c>
       <c r="B37" t="n">
-        <v>79936</v>
+        <v>79319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411743</v>
+        <v>411775</v>
       </c>
       <c r="R37" t="n">
-        <v>6706033</v>
+        <v>6706079</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132519432</v>
+        <v>132519405</v>
       </c>
       <c r="B38" t="n">
-        <v>79317</v>
+        <v>79077</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411775</v>
+        <v>411830</v>
       </c>
       <c r="R38" t="n">
-        <v>6706079</v>
+        <v>6706163</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132519405</v>
+        <v>132519408</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411830</v>
+        <v>411867</v>
       </c>
       <c r="R39" t="n">
-        <v>6706163</v>
+        <v>6706121</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4455,7 +4455,7 @@
         <v>132519388</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519374</v>
+        <v>132519411</v>
       </c>
       <c r="B41" t="n">
-        <v>79936</v>
+        <v>79077</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411937</v>
+        <v>411909</v>
       </c>
       <c r="R41" t="n">
-        <v>6706170</v>
+        <v>6706115</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519370</v>
+        <v>132519374</v>
       </c>
       <c r="B42" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411829</v>
+        <v>411937</v>
       </c>
       <c r="R42" t="n">
-        <v>6706165</v>
+        <v>6706170</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519411</v>
+        <v>132519370</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79938</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411909</v>
+        <v>411829</v>
       </c>
       <c r="R43" t="n">
-        <v>6706115</v>
+        <v>6706165</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>132640387</v>
       </c>
       <c r="B44" t="n">
-        <v>81302</v>
+        <v>81304</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>132640080</v>
       </c>
       <c r="B45" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>132640284</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>132640439</v>
       </c>
       <c r="B47" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>132640452</v>
       </c>
       <c r="B48" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132639607</v>
+        <v>132640069</v>
       </c>
       <c r="B49" t="n">
-        <v>83289</v>
+        <v>79319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,21 +5336,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411648</v>
+        <v>411560</v>
       </c>
       <c r="R49" t="n">
-        <v>6705948</v>
+        <v>6705975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5425,7 +5425,7 @@
         <v>132639955</v>
       </c>
       <c r="B50" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132640069</v>
+        <v>132639607</v>
       </c>
       <c r="B51" t="n">
-        <v>79317</v>
+        <v>83291</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411560</v>
+        <v>411648</v>
       </c>
       <c r="R51" t="n">
-        <v>6705975</v>
+        <v>6705948</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5619,7 +5619,7 @@
         <v>132640306</v>
       </c>
       <c r="B52" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5713,10 +5713,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132639985</v>
+        <v>132639564</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>83291</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5724,21 +5724,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>411571</v>
+        <v>411663</v>
       </c>
       <c r="R53" t="n">
-        <v>6705940</v>
+        <v>6705970</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5810,10 +5810,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132639564</v>
+        <v>132639985</v>
       </c>
       <c r="B54" t="n">
-        <v>83289</v>
+        <v>79077</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5821,21 +5821,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411663</v>
+        <v>411571</v>
       </c>
       <c r="R54" t="n">
-        <v>6705970</v>
+        <v>6705940</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5910,7 +5910,7 @@
         <v>132640187</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>132640049</v>
       </c>
       <c r="B56" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>132641415</v>
       </c>
       <c r="B57" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>132640952</v>
       </c>
       <c r="B58" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6292,6 +6292,5357 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132662718</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>411446</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6705831</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>5 olika träd</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>David Schinkler</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132667028</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57949</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sörsjön Väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>411614</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6705987</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132667709</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78722</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>411556</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6705948</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132667685</v>
+      </c>
+      <c r="B62" t="n">
+        <v>81304</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>411469</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6705915</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132667666</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>411560</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6705963</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132662722</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>411632</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6705947</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 olika träd</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>David Schinkler</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132667676</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>411584</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6705901</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132667684</v>
+      </c>
+      <c r="B66" t="n">
+        <v>81304</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>411558</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6705956</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132667674</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>411561</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6705875</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132667660</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>411618</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6705941</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132667703</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78985</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>353</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>411563</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6705954</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132667648</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>185</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>411942</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6706149</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132667692</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>411772</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6706080</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132667695</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>411665</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6706009</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132667649</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79938</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>411618</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6705989</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132667691</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>411468</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6705919</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132667693</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>411806</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6706080</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132667665</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>411618</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6705988</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132667708</v>
+      </c>
+      <c r="B77" t="n">
+        <v>83291</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>308</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>411883</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6706128</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132662725</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>411718</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6706075</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>10 olika träd</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>David Schinkler</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132662723</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>411667</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6705978</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>David Schinkler</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132667029</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57137</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sörsjön Väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>411607</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6705981</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132667675</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>411580</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6705883</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>132667658</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57137</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>411492</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6705892</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132662721</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>411557</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6705880</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>2 olika träd</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>David Schinkler</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132667656</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79938</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>411711</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6706080</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132667672</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>411476</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6705898</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132667694</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>411516</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6705918</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132667661</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80328</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>411625</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6705944</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>132667696</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>411674</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6706071</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132667707</v>
+      </c>
+      <c r="B89" t="n">
+        <v>83291</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>308</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>411675</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6705969</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>132667688</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80384</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>411633</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6705944</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132667655</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79938</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>411610</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6705914</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>132667664</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>411617</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6705992</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132667705</v>
+      </c>
+      <c r="B93" t="n">
+        <v>78985</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>353</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>411596</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6705928</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>132667654</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79938</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>411588</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6705893</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>132667652</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79938</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>411468</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6705902</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>132667710</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91955</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>411642</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6705943</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132662719</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>411464</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6705854</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>David Schinkler</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>132667678</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>411584</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6705909</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132667033</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sörsjön Väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>411635</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6705944</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>132667687</v>
+      </c>
+      <c r="B100" t="n">
+        <v>81304</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>411758</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6706085</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>132667673</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>411487</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6705896</v>
+      </c>
+      <c r="S101" t="n">
+        <v>25</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>132667680</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>411869</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6706115</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>132667651</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79938</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>411563</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6705952</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>132667650</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79938</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>411618</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6705988</v>
+      </c>
+      <c r="S104" t="n">
+        <v>25</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>132667686</v>
+      </c>
+      <c r="B105" t="n">
+        <v>81304</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>411716</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6706077</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>132667653</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79938</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>411515</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6705902</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>132667679</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79077</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>411585</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6705911</v>
+      </c>
+      <c r="S107" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>132667698</v>
+      </c>
+      <c r="B108" t="n">
+        <v>83165</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>411666</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6706009</v>
+      </c>
+      <c r="S108" t="n">
+        <v>25</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>132667690</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>411525</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6705921</v>
+      </c>
+      <c r="S109" t="n">
+        <v>25</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>132667663</v>
+      </c>
+      <c r="B110" t="n">
+        <v>91951</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>411576</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6705886</v>
+      </c>
+      <c r="S110" t="n">
+        <v>25</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>132667662</v>
+      </c>
+      <c r="B111" t="n">
+        <v>91951</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>411595</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6705935</v>
+      </c>
+      <c r="S111" t="n">
+        <v>25</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>132667706</v>
+      </c>
+      <c r="B112" t="n">
+        <v>78985</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>353</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Gästgivartjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>411713</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6706084</v>
+      </c>
+      <c r="S112" t="n">
+        <v>25</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -3579,32 +3579,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132519394</v>
+        <v>132519376</v>
       </c>
       <c r="B31" t="n">
-        <v>79077</v>
+        <v>79405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411741</v>
+        <v>411939</v>
       </c>
       <c r="R31" t="n">
-        <v>6706031</v>
+        <v>6706156</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132519413</v>
+        <v>132519394</v>
       </c>
       <c r="B32" t="n">
         <v>79077</v>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411921</v>
+        <v>411741</v>
       </c>
       <c r="R32" t="n">
-        <v>6706127</v>
+        <v>6706031</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3773,32 +3773,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132519376</v>
+        <v>132519413</v>
       </c>
       <c r="B33" t="n">
-        <v>79405</v>
+        <v>79077</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411939</v>
+        <v>411921</v>
       </c>
       <c r="R33" t="n">
-        <v>6706156</v>
+        <v>6706127</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132662718</v>
+        <v>132667709</v>
       </c>
       <c r="B59" t="n">
-        <v>79319</v>
+        <v>78722</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6306,44 +6306,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>411446</v>
+        <v>411556</v>
       </c>
       <c r="R59" t="n">
-        <v>6705831</v>
+        <v>6705948</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6375,40 +6368,34 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>5 olika träd</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132667028</v>
+        <v>132662718</v>
       </c>
       <c r="B60" t="n">
-        <v>57949</v>
+        <v>79319</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6416,42 +6403,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411614</v>
+        <v>411446</v>
       </c>
       <c r="R60" t="n">
-        <v>6705987</v>
+        <v>6705831</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6486,34 +6472,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>5 olika träd</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132667709</v>
+        <v>132667028</v>
       </c>
       <c r="B61" t="n">
-        <v>78722</v>
+        <v>57949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6521,37 +6513,45 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411556</v>
+        <v>411614</v>
       </c>
       <c r="R61" t="n">
-        <v>6705948</v>
+        <v>6705987</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132667666</v>
+        <v>132662722</v>
       </c>
       <c r="B63" t="n">
-        <v>79077</v>
+        <v>79319</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6715,37 +6715,44 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411560</v>
+        <v>411632</v>
       </c>
       <c r="R63" t="n">
-        <v>6705963</v>
+        <v>6705947</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6777,34 +6784,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>3 olika träd</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132662722</v>
+        <v>132667666</v>
       </c>
       <c r="B64" t="n">
-        <v>79319</v>
+        <v>79077</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6812,44 +6825,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411632</v>
+        <v>411560</v>
       </c>
       <c r="R64" t="n">
-        <v>6705947</v>
+        <v>6705963</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6881,30 +6887,24 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>3 olika träd</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132667694</v>
+        <v>132667707</v>
       </c>
       <c r="B86" t="n">
-        <v>79319</v>
+        <v>83291</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9013,21 +9013,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>411516</v>
+        <v>411675</v>
       </c>
       <c r="R86" t="n">
-        <v>6705918</v>
+        <v>6705969</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9099,32 +9099,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132667661</v>
+        <v>132667694</v>
       </c>
       <c r="B87" t="n">
-        <v>80328</v>
+        <v>79319</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>411625</v>
+        <v>411516</v>
       </c>
       <c r="R87" t="n">
-        <v>6705944</v>
+        <v>6705918</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9196,32 +9196,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132667696</v>
+        <v>132667661</v>
       </c>
       <c r="B88" t="n">
-        <v>79319</v>
+        <v>80328</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>411674</v>
+        <v>411625</v>
       </c>
       <c r="R88" t="n">
-        <v>6706071</v>
+        <v>6705944</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9293,10 +9293,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132667707</v>
+        <v>132667696</v>
       </c>
       <c r="B89" t="n">
-        <v>83291</v>
+        <v>79319</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9304,21 +9304,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>411675</v>
+        <v>411674</v>
       </c>
       <c r="R89" t="n">
-        <v>6705969</v>
+        <v>6706071</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9980,48 +9980,51 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132667710</v>
+        <v>132662719</v>
       </c>
       <c r="B96" t="n">
-        <v>91955</v>
+        <v>79319</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>411642</v>
+        <v>411464</v>
       </c>
       <c r="R96" t="n">
-        <v>6705943</v>
+        <v>6705854</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10066,22 +10069,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132662719</v>
+        <v>132667678</v>
       </c>
       <c r="B97" t="n">
-        <v>79319</v>
+        <v>79077</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10089,40 +10092,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>411464</v>
+        <v>411584</v>
       </c>
       <c r="R97" t="n">
-        <v>6705854</v>
+        <v>6705909</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10160,51 +10160,50 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132667678</v>
+        <v>132667710</v>
       </c>
       <c r="B98" t="n">
-        <v>79077</v>
+        <v>91955</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>5321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10214,10 +10213,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>411584</v>
+        <v>411642</v>
       </c>
       <c r="R98" t="n">
-        <v>6705909</v>
+        <v>6705943</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10258,6 +10257,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11064,10 +11064,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132667679</v>
+        <v>132667690</v>
       </c>
       <c r="B107" t="n">
-        <v>79077</v>
+        <v>79319</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11075,21 +11075,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411585</v>
+        <v>411525</v>
       </c>
       <c r="R107" t="n">
-        <v>6705911</v>
+        <v>6705921</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11161,10 +11161,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132667698</v>
+        <v>132667679</v>
       </c>
       <c r="B108" t="n">
-        <v>83165</v>
+        <v>79077</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411666</v>
+        <v>411585</v>
       </c>
       <c r="R108" t="n">
-        <v>6706009</v>
+        <v>6705911</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132667690</v>
+        <v>132667698</v>
       </c>
       <c r="B109" t="n">
-        <v>79319</v>
+        <v>83165</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11269,21 +11269,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>411525</v>
+        <v>411666</v>
       </c>
       <c r="R109" t="n">
-        <v>6705921</v>
+        <v>6706009</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132519362</v>
+        <v>132514331</v>
       </c>
       <c r="B8" t="n">
-        <v>79938</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,37 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411626</v>
+        <v>411764</v>
       </c>
       <c r="R8" t="n">
-        <v>6705988</v>
+        <v>6706079</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132519427</v>
+        <v>132519362</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411777</v>
+        <v>411626</v>
       </c>
       <c r="R9" t="n">
-        <v>6706085</v>
+        <v>6705988</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132514331</v>
+        <v>132519427</v>
       </c>
       <c r="B10" t="n">
-        <v>81304</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,37 +1552,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411764</v>
+        <v>411777</v>
       </c>
       <c r="R10" t="n">
-        <v>6706079</v>
+        <v>6706085</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,12 +1626,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1641,7 +1641,7 @@
         <v>132519415</v>
       </c>
       <c r="B11" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>132519436</v>
       </c>
       <c r="B12" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>132519431</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>132519365</v>
       </c>
       <c r="B14" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132519422</v>
       </c>
       <c r="B15" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>132519433</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>132519367</v>
       </c>
       <c r="B17" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>132519396</v>
       </c>
       <c r="B18" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>132519403</v>
       </c>
       <c r="B19" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>132519428</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>132519424</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>132519372</v>
       </c>
       <c r="B22" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>132514329</v>
       </c>
       <c r="B23" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>132519400</v>
       </c>
       <c r="B24" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>132519418</v>
       </c>
       <c r="B25" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>132519392</v>
       </c>
       <c r="B26" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>132519398</v>
       </c>
       <c r="B27" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132519430</v>
+        <v>132519435</v>
       </c>
       <c r="B28" t="n">
-        <v>79319</v>
+        <v>78993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3299,21 +3299,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>411592</v>
+        <v>411612</v>
       </c>
       <c r="R28" t="n">
-        <v>6705990</v>
+        <v>6705977</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132519435</v>
+        <v>132519430</v>
       </c>
       <c r="B29" t="n">
-        <v>78985</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3396,21 +3396,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411612</v>
+        <v>411592</v>
       </c>
       <c r="R29" t="n">
-        <v>6705977</v>
+        <v>6705990</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3485,7 +3485,7 @@
         <v>132519390</v>
       </c>
       <c r="B30" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3579,32 +3579,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132519376</v>
+        <v>132519394</v>
       </c>
       <c r="B31" t="n">
-        <v>79405</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411939</v>
+        <v>411741</v>
       </c>
       <c r="R31" t="n">
-        <v>6706156</v>
+        <v>6706031</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132519394</v>
+        <v>132519413</v>
       </c>
       <c r="B32" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411741</v>
+        <v>411921</v>
       </c>
       <c r="R32" t="n">
-        <v>6706031</v>
+        <v>6706127</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3773,32 +3773,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132519413</v>
+        <v>132519376</v>
       </c>
       <c r="B33" t="n">
-        <v>79077</v>
+        <v>79413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411921</v>
+        <v>411939</v>
       </c>
       <c r="R33" t="n">
-        <v>6706127</v>
+        <v>6706156</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3873,7 +3873,7 @@
         <v>132514332</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>132519364</v>
       </c>
       <c r="B35" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>132514333</v>
       </c>
       <c r="B36" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>132519432</v>
       </c>
       <c r="B37" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>132519405</v>
       </c>
       <c r="B38" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>132519408</v>
       </c>
       <c r="B39" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>132519388</v>
       </c>
       <c r="B40" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519411</v>
+        <v>132519374</v>
       </c>
       <c r="B41" t="n">
-        <v>79077</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411909</v>
+        <v>411937</v>
       </c>
       <c r="R41" t="n">
-        <v>6706115</v>
+        <v>6706170</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519374</v>
+        <v>132519370</v>
       </c>
       <c r="B42" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411937</v>
+        <v>411829</v>
       </c>
       <c r="R42" t="n">
-        <v>6706170</v>
+        <v>6706165</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519370</v>
+        <v>132519411</v>
       </c>
       <c r="B43" t="n">
-        <v>79938</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411829</v>
+        <v>411909</v>
       </c>
       <c r="R43" t="n">
-        <v>6706165</v>
+        <v>6706115</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>132640387</v>
       </c>
       <c r="B44" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>132640080</v>
       </c>
       <c r="B45" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>132640284</v>
       </c>
       <c r="B46" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>132640439</v>
       </c>
       <c r="B47" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>132640452</v>
       </c>
       <c r="B48" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132640069</v>
+        <v>132639607</v>
       </c>
       <c r="B49" t="n">
-        <v>79319</v>
+        <v>83299</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,21 +5336,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411560</v>
+        <v>411648</v>
       </c>
       <c r="R49" t="n">
-        <v>6705975</v>
+        <v>6705948</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5425,7 +5425,7 @@
         <v>132639955</v>
       </c>
       <c r="B50" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132639607</v>
+        <v>132640069</v>
       </c>
       <c r="B51" t="n">
-        <v>83291</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411648</v>
+        <v>411560</v>
       </c>
       <c r="R51" t="n">
-        <v>6705948</v>
+        <v>6705975</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5619,7 +5619,7 @@
         <v>132640306</v>
       </c>
       <c r="B52" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>132639564</v>
       </c>
       <c r="B53" t="n">
-        <v>83291</v>
+        <v>83299</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>132639985</v>
       </c>
       <c r="B54" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5907,10 +5907,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132640187</v>
+        <v>132640049</v>
       </c>
       <c r="B55" t="n">
-        <v>79077</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,21 +5918,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411549</v>
+        <v>411557</v>
       </c>
       <c r="R55" t="n">
-        <v>6705962</v>
+        <v>6705961</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132640049</v>
+        <v>132640187</v>
       </c>
       <c r="B56" t="n">
-        <v>79938</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411557</v>
+        <v>411549</v>
       </c>
       <c r="R56" t="n">
-        <v>6705961</v>
+        <v>6705962</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
         <v>132641415</v>
       </c>
       <c r="B57" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>132640952</v>
       </c>
       <c r="B58" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132667709</v>
+        <v>132662718</v>
       </c>
       <c r="B59" t="n">
-        <v>78722</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6306,37 +6306,44 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>411556</v>
+        <v>411446</v>
       </c>
       <c r="R59" t="n">
-        <v>6705948</v>
+        <v>6705831</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6368,34 +6375,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>5 olika träd</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132662718</v>
+        <v>132667709</v>
       </c>
       <c r="B60" t="n">
-        <v>79319</v>
+        <v>78730</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6403,44 +6416,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411446</v>
+        <v>411556</v>
       </c>
       <c r="R60" t="n">
-        <v>6705831</v>
+        <v>6705948</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6472,30 +6478,24 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>5 olika träd</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6505,7 +6505,7 @@
         <v>132667028</v>
       </c>
       <c r="B61" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>132667685</v>
       </c>
       <c r="B62" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>132662722</v>
       </c>
       <c r="B63" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>132667666</v>
       </c>
       <c r="B64" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>132667676</v>
       </c>
       <c r="B65" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>132667684</v>
       </c>
       <c r="B66" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>132667674</v>
       </c>
       <c r="B67" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>132667660</v>
       </c>
       <c r="B68" t="n">
-        <v>79405</v>
+        <v>79413</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132667703</v>
+        <v>132667692</v>
       </c>
       <c r="B69" t="n">
-        <v>78985</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411563</v>
+        <v>411772</v>
       </c>
       <c r="R69" t="n">
-        <v>6705954</v>
+        <v>6706080</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7396,10 +7396,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132667648</v>
+        <v>132667703</v>
       </c>
       <c r="B70" t="n">
-        <v>79351</v>
+        <v>78993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7407,37 +7407,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411942</v>
+        <v>411563</v>
       </c>
       <c r="R70" t="n">
-        <v>6706149</v>
+        <v>6705954</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7478,7 +7475,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7497,10 +7493,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132667692</v>
+        <v>132667648</v>
       </c>
       <c r="B71" t="n">
-        <v>79319</v>
+        <v>79359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7508,34 +7504,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411772</v>
+        <v>411942</v>
       </c>
       <c r="R71" t="n">
-        <v>6706080</v>
+        <v>6706149</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7576,6 +7575,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7597,7 +7597,7 @@
         <v>132667695</v>
       </c>
       <c r="B72" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>132667649</v>
       </c>
       <c r="B73" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>132667691</v>
       </c>
       <c r="B74" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132667693</v>
+        <v>132667708</v>
       </c>
       <c r="B75" t="n">
-        <v>79319</v>
+        <v>83299</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411806</v>
+        <v>411883</v>
       </c>
       <c r="R75" t="n">
-        <v>6706080</v>
+        <v>6706128</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132667665</v>
+        <v>132667693</v>
       </c>
       <c r="B76" t="n">
-        <v>79077</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>411618</v>
+        <v>411806</v>
       </c>
       <c r="R76" t="n">
-        <v>6705988</v>
+        <v>6706080</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132667708</v>
+        <v>132667665</v>
       </c>
       <c r="B77" t="n">
-        <v>83291</v>
+        <v>79085</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8094,21 +8094,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>411883</v>
+        <v>411618</v>
       </c>
       <c r="R77" t="n">
-        <v>6706128</v>
+        <v>6705988</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8183,7 +8183,7 @@
         <v>132662725</v>
       </c>
       <c r="B78" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>132662723</v>
       </c>
       <c r="B79" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8391,10 +8391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132667029</v>
+        <v>132667658</v>
       </c>
       <c r="B80" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8424,23 +8424,23 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411607</v>
+        <v>411492</v>
       </c>
       <c r="R80" t="n">
-        <v>6705981</v>
+        <v>6705892</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8484,60 +8484,68 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132667675</v>
+        <v>132667029</v>
       </c>
       <c r="B81" t="n">
-        <v>79077</v>
+        <v>57141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>411580</v>
+        <v>411607</v>
       </c>
       <c r="R81" t="n">
-        <v>6705883</v>
+        <v>6705981</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8581,65 +8589,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132667658</v>
+        <v>132667675</v>
       </c>
       <c r="B82" t="n">
-        <v>57137</v>
+        <v>79085</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>411492</v>
+        <v>411580</v>
       </c>
       <c r="R82" t="n">
-        <v>6705892</v>
+        <v>6705883</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8701,7 +8701,7 @@
         <v>132662721</v>
       </c>
       <c r="B83" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>132667656</v>
       </c>
       <c r="B84" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>132667672</v>
       </c>
       <c r="B85" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>132667707</v>
       </c>
       <c r="B86" t="n">
-        <v>83291</v>
+        <v>83299</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>132667694</v>
       </c>
       <c r="B87" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>132667661</v>
       </c>
       <c r="B88" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>132667696</v>
       </c>
       <c r="B89" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9390,32 +9390,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132667688</v>
+        <v>132667705</v>
       </c>
       <c r="B90" t="n">
-        <v>80384</v>
+        <v>78993</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>411633</v>
+        <v>411596</v>
       </c>
       <c r="R90" t="n">
-        <v>6705944</v>
+        <v>6705928</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9490,7 +9490,7 @@
         <v>132667655</v>
       </c>
       <c r="B91" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9584,32 +9584,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132667664</v>
+        <v>132667688</v>
       </c>
       <c r="B92" t="n">
-        <v>79077</v>
+        <v>80392</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9619,10 +9619,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>411617</v>
+        <v>411633</v>
       </c>
       <c r="R92" t="n">
-        <v>6705992</v>
+        <v>6705944</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9681,10 +9681,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667705</v>
+        <v>132667664</v>
       </c>
       <c r="B93" t="n">
-        <v>78985</v>
+        <v>79085</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9692,21 +9692,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411596</v>
+        <v>411617</v>
       </c>
       <c r="R93" t="n">
-        <v>6705928</v>
+        <v>6705992</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9778,48 +9778,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132667654</v>
+        <v>132667710</v>
       </c>
       <c r="B94" t="n">
-        <v>79938</v>
+        <v>91965</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>5321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>411588</v>
+        <v>411642</v>
       </c>
       <c r="R94" t="n">
-        <v>6705893</v>
+        <v>6705943</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -9872,17 +9869,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132667652</v>
+        <v>132667654</v>
       </c>
       <c r="B95" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9917,10 +9914,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>411468</v>
+        <v>411588</v>
       </c>
       <c r="R95" t="n">
-        <v>6705902</v>
+        <v>6705893</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -9980,10 +9977,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132662719</v>
+        <v>132667652</v>
       </c>
       <c r="B96" t="n">
-        <v>79319</v>
+        <v>79946</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9991,21 +9988,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10018,13 +10015,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>411464</v>
+        <v>411468</v>
       </c>
       <c r="R96" t="n">
-        <v>6705854</v>
+        <v>6705902</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10069,22 +10066,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132667678</v>
+        <v>132662719</v>
       </c>
       <c r="B97" t="n">
-        <v>79077</v>
+        <v>79327</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10092,37 +10089,40 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>411584</v>
+        <v>411464</v>
       </c>
       <c r="R97" t="n">
-        <v>6705909</v>
+        <v>6705854</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10160,50 +10160,51 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132667710</v>
+        <v>132667678</v>
       </c>
       <c r="B98" t="n">
-        <v>91955</v>
+        <v>79085</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5321</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10213,10 +10214,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>411642</v>
+        <v>411584</v>
       </c>
       <c r="R98" t="n">
-        <v>6705943</v>
+        <v>6705909</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10257,7 +10258,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10269,17 +10269,17 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132667033</v>
+        <v>132667687</v>
       </c>
       <c r="B99" t="n">
-        <v>79319</v>
+        <v>81312</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10287,37 +10287,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411635</v>
+        <v>411758</v>
       </c>
       <c r="R99" t="n">
-        <v>6705944</v>
+        <v>6706085</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10361,22 +10361,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132667687</v>
+        <v>132667033</v>
       </c>
       <c r="B100" t="n">
-        <v>81304</v>
+        <v>79327</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,37 +10384,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411758</v>
+        <v>411635</v>
       </c>
       <c r="R100" t="n">
-        <v>6706085</v>
+        <v>6705944</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10458,12 +10458,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10473,7 +10473,7 @@
         <v>132667673</v>
       </c>
       <c r="B101" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>132667680</v>
       </c>
       <c r="B102" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10664,10 +10664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132667651</v>
+        <v>132667686</v>
       </c>
       <c r="B103" t="n">
-        <v>79938</v>
+        <v>81312</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10675,37 +10675,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411563</v>
+        <v>411716</v>
       </c>
       <c r="R103" t="n">
-        <v>6705952</v>
+        <v>6706077</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -10746,7 +10743,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10765,10 +10761,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132667650</v>
+        <v>132667651</v>
       </c>
       <c r="B104" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10803,10 +10799,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411618</v>
+        <v>411563</v>
       </c>
       <c r="R104" t="n">
-        <v>6705988</v>
+        <v>6705952</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -10866,10 +10862,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132667686</v>
+        <v>132667650</v>
       </c>
       <c r="B105" t="n">
-        <v>81304</v>
+        <v>79946</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10877,34 +10873,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>411716</v>
+        <v>411618</v>
       </c>
       <c r="R105" t="n">
-        <v>6706077</v>
+        <v>6705988</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -10945,6 +10944,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>132667653</v>
       </c>
       <c r="B106" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11064,10 +11064,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132667690</v>
+        <v>132667679</v>
       </c>
       <c r="B107" t="n">
-        <v>79319</v>
+        <v>79085</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11075,21 +11075,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411525</v>
+        <v>411585</v>
       </c>
       <c r="R107" t="n">
-        <v>6705921</v>
+        <v>6705911</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11161,10 +11161,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132667679</v>
+        <v>132667698</v>
       </c>
       <c r="B108" t="n">
-        <v>79077</v>
+        <v>83173</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411585</v>
+        <v>411666</v>
       </c>
       <c r="R108" t="n">
-        <v>6705911</v>
+        <v>6706009</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132667698</v>
+        <v>132667690</v>
       </c>
       <c r="B109" t="n">
-        <v>83165</v>
+        <v>79327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11269,21 +11269,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>411666</v>
+        <v>411525</v>
       </c>
       <c r="R109" t="n">
-        <v>6706009</v>
+        <v>6705921</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11355,10 +11355,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132667663</v>
+        <v>132667706</v>
       </c>
       <c r="B110" t="n">
-        <v>91951</v>
+        <v>78993</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11366,21 +11366,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411576</v>
+        <v>411713</v>
       </c>
       <c r="R110" t="n">
-        <v>6705886</v>
+        <v>6706084</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11452,10 +11452,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132667662</v>
+        <v>132667663</v>
       </c>
       <c r="B111" t="n">
-        <v>91951</v>
+        <v>91961</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11487,10 +11487,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411595</v>
+        <v>411576</v>
       </c>
       <c r="R111" t="n">
-        <v>6705935</v>
+        <v>6705886</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11549,10 +11549,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132667706</v>
+        <v>132667662</v>
       </c>
       <c r="B112" t="n">
-        <v>78985</v>
+        <v>91961</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11560,21 +11560,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11584,10 +11584,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411713</v>
+        <v>411595</v>
       </c>
       <c r="R112" t="n">
-        <v>6706084</v>
+        <v>6705935</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132514331</v>
+        <v>132519362</v>
       </c>
       <c r="B8" t="n">
-        <v>81312</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,37 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411764</v>
+        <v>411626</v>
       </c>
       <c r="R8" t="n">
-        <v>6706079</v>
+        <v>6705988</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132519362</v>
+        <v>132514331</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,37 +1455,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411626</v>
+        <v>411764</v>
       </c>
       <c r="R9" t="n">
-        <v>6705988</v>
+        <v>6706079</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,12 +1529,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132519367</v>
+        <v>132519396</v>
       </c>
       <c r="B17" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,21 +2232,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411782</v>
+        <v>411744</v>
       </c>
       <c r="R17" t="n">
-        <v>6706088</v>
+        <v>6706031</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132519396</v>
+        <v>132519403</v>
       </c>
       <c r="B18" t="n">
         <v>79085</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411744</v>
+        <v>411785</v>
       </c>
       <c r="R18" t="n">
-        <v>6706031</v>
+        <v>6706078</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132519403</v>
+        <v>132519367</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411785</v>
+        <v>411782</v>
       </c>
       <c r="R19" t="n">
-        <v>6706078</v>
+        <v>6706088</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132514332</v>
+        <v>132519405</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,37 +3881,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411910</v>
+        <v>411830</v>
       </c>
       <c r="R34" t="n">
-        <v>6706124</v>
+        <v>6706163</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132519364</v>
+        <v>132519408</v>
       </c>
       <c r="B35" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411743</v>
+        <v>411867</v>
       </c>
       <c r="R35" t="n">
-        <v>6706033</v>
+        <v>6706121</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132514333</v>
+        <v>132519388</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,37 +4075,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411597</v>
+        <v>411615</v>
       </c>
       <c r="R36" t="n">
-        <v>6705968</v>
+        <v>6705973</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132519432</v>
+        <v>132514332</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,37 +4172,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411775</v>
+        <v>411910</v>
       </c>
       <c r="R37" t="n">
-        <v>6706079</v>
+        <v>6706124</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132519405</v>
+        <v>132519364</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411830</v>
+        <v>411743</v>
       </c>
       <c r="R38" t="n">
-        <v>6706163</v>
+        <v>6706033</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132519408</v>
+        <v>132514333</v>
       </c>
       <c r="B39" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,37 +4366,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411867</v>
+        <v>411597</v>
       </c>
       <c r="R39" t="n">
-        <v>6706121</v>
+        <v>6705968</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4440,22 +4440,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132519388</v>
+        <v>132519432</v>
       </c>
       <c r="B40" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411615</v>
+        <v>411775</v>
       </c>
       <c r="R40" t="n">
-        <v>6705973</v>
+        <v>6706079</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519374</v>
+        <v>132519411</v>
       </c>
       <c r="B41" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411937</v>
+        <v>411909</v>
       </c>
       <c r="R41" t="n">
-        <v>6706170</v>
+        <v>6706115</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519370</v>
+        <v>132519374</v>
       </c>
       <c r="B42" t="n">
         <v>79946</v>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411829</v>
+        <v>411937</v>
       </c>
       <c r="R42" t="n">
-        <v>6706165</v>
+        <v>6706170</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519411</v>
+        <v>132519370</v>
       </c>
       <c r="B43" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411909</v>
+        <v>411829</v>
       </c>
       <c r="R43" t="n">
-        <v>6706115</v>
+        <v>6706165</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132639955</v>
+        <v>132640069</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411559</v>
+        <v>411560</v>
       </c>
       <c r="R50" t="n">
-        <v>6705948</v>
+        <v>6705975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5519,7 +5519,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132640069</v>
+        <v>132639955</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411560</v>
+        <v>411559</v>
       </c>
       <c r="R51" t="n">
-        <v>6705975</v>
+        <v>6705948</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5907,10 +5907,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132640049</v>
+        <v>132640187</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,21 +5918,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411557</v>
+        <v>411549</v>
       </c>
       <c r="R55" t="n">
-        <v>6705961</v>
+        <v>6705962</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132640187</v>
+        <v>132640049</v>
       </c>
       <c r="B56" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411549</v>
+        <v>411557</v>
       </c>
       <c r="R56" t="n">
-        <v>6705962</v>
+        <v>6705961</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132662722</v>
+        <v>132667666</v>
       </c>
       <c r="B63" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6715,44 +6715,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411632</v>
+        <v>411560</v>
       </c>
       <c r="R63" t="n">
-        <v>6705947</v>
+        <v>6705963</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6784,40 +6777,34 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>3 olika träd</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132667666</v>
+        <v>132662722</v>
       </c>
       <c r="B64" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6825,37 +6812,44 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411560</v>
+        <v>411632</v>
       </c>
       <c r="R64" t="n">
-        <v>6705963</v>
+        <v>6705947</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6887,24 +6881,30 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 olika träd</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7202,32 +7202,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132667660</v>
+        <v>132667703</v>
       </c>
       <c r="B68" t="n">
-        <v>79413</v>
+        <v>78993</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411618</v>
+        <v>411563</v>
       </c>
       <c r="R68" t="n">
-        <v>6705941</v>
+        <v>6705954</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132667692</v>
+        <v>132667648</v>
       </c>
       <c r="B69" t="n">
-        <v>79327</v>
+        <v>79359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,34 +7310,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411772</v>
+        <v>411942</v>
       </c>
       <c r="R69" t="n">
-        <v>6706080</v>
+        <v>6706149</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7378,6 +7381,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7396,32 +7400,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132667703</v>
+        <v>132667660</v>
       </c>
       <c r="B70" t="n">
-        <v>78993</v>
+        <v>79413</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6450</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7431,10 +7435,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411563</v>
+        <v>411618</v>
       </c>
       <c r="R70" t="n">
-        <v>6705954</v>
+        <v>6705941</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7493,10 +7497,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132667648</v>
+        <v>132667692</v>
       </c>
       <c r="B71" t="n">
-        <v>79359</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,37 +7508,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411942</v>
+        <v>411772</v>
       </c>
       <c r="R71" t="n">
-        <v>6706149</v>
+        <v>6706080</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7575,7 +7576,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8180,55 +8180,56 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132662725</v>
+        <v>132667029</v>
       </c>
       <c r="B78" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411718</v>
+        <v>411607</v>
       </c>
       <c r="R78" t="n">
-        <v>6706075</v>
+        <v>6705981</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8260,67 +8261,66 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>10 olika träd</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132662723</v>
+        <v>132667658</v>
       </c>
       <c r="B79" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>411667</v>
+        <v>411492</v>
       </c>
       <c r="R79" t="n">
-        <v>6705978</v>
+        <v>6705892</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8372,61 +8372,59 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132667658</v>
+        <v>132662725</v>
       </c>
       <c r="B80" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8434,13 +8432,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411492</v>
+        <v>411718</v>
       </c>
       <c r="R80" t="n">
-        <v>6705892</v>
+        <v>6706075</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8472,80 +8470,81 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>10 olika träd</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132667029</v>
+        <v>132662723</v>
       </c>
       <c r="B81" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>411607</v>
+        <v>411667</v>
       </c>
       <c r="R81" t="n">
-        <v>6705981</v>
+        <v>6705978</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8583,18 +8582,19 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9390,32 +9390,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132667705</v>
+        <v>132667688</v>
       </c>
       <c r="B90" t="n">
-        <v>78993</v>
+        <v>80392</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>411596</v>
+        <v>411633</v>
       </c>
       <c r="R90" t="n">
-        <v>6705928</v>
+        <v>6705944</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132667655</v>
+        <v>132667664</v>
       </c>
       <c r="B91" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9498,21 +9498,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>411610</v>
+        <v>411617</v>
       </c>
       <c r="R91" t="n">
-        <v>6705914</v>
+        <v>6705992</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9584,32 +9584,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132667688</v>
+        <v>132667705</v>
       </c>
       <c r="B92" t="n">
-        <v>80392</v>
+        <v>78993</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9619,10 +9619,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>411633</v>
+        <v>411596</v>
       </c>
       <c r="R92" t="n">
-        <v>6705944</v>
+        <v>6705928</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9681,10 +9681,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667664</v>
+        <v>132667655</v>
       </c>
       <c r="B93" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9692,21 +9692,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411617</v>
+        <v>411610</v>
       </c>
       <c r="R93" t="n">
-        <v>6705992</v>
+        <v>6705914</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9781,7 +9781,7 @@
         <v>132667710</v>
       </c>
       <c r="B94" t="n">
-        <v>91965</v>
+        <v>91966</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132667687</v>
+        <v>132667033</v>
       </c>
       <c r="B99" t="n">
-        <v>81312</v>
+        <v>79327</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10287,37 +10287,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411758</v>
+        <v>411635</v>
       </c>
       <c r="R99" t="n">
-        <v>6706085</v>
+        <v>6705944</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10361,22 +10361,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132667033</v>
+        <v>132667687</v>
       </c>
       <c r="B100" t="n">
-        <v>79327</v>
+        <v>81312</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,37 +10384,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411635</v>
+        <v>411758</v>
       </c>
       <c r="R100" t="n">
-        <v>6705944</v>
+        <v>6706085</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10458,12 +10458,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10664,10 +10664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132667686</v>
+        <v>132667651</v>
       </c>
       <c r="B103" t="n">
-        <v>81312</v>
+        <v>79946</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10675,34 +10675,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411716</v>
+        <v>411563</v>
       </c>
       <c r="R103" t="n">
-        <v>6706077</v>
+        <v>6705952</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -10743,6 +10746,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10761,7 +10765,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132667651</v>
+        <v>132667650</v>
       </c>
       <c r="B104" t="n">
         <v>79946</v>
@@ -10799,10 +10803,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411563</v>
+        <v>411618</v>
       </c>
       <c r="R104" t="n">
-        <v>6705952</v>
+        <v>6705988</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -10862,10 +10866,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132667650</v>
+        <v>132667686</v>
       </c>
       <c r="B105" t="n">
-        <v>79946</v>
+        <v>81312</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10873,37 +10877,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>411618</v>
+        <v>411716</v>
       </c>
       <c r="R105" t="n">
-        <v>6705988</v>
+        <v>6706077</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -10944,7 +10945,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11064,10 +11064,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132667679</v>
+        <v>132667698</v>
       </c>
       <c r="B107" t="n">
-        <v>79085</v>
+        <v>83173</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11075,21 +11075,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411585</v>
+        <v>411666</v>
       </c>
       <c r="R107" t="n">
-        <v>6705911</v>
+        <v>6706009</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11161,10 +11161,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132667698</v>
+        <v>132667690</v>
       </c>
       <c r="B108" t="n">
-        <v>83173</v>
+        <v>79327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411666</v>
+        <v>411525</v>
       </c>
       <c r="R108" t="n">
-        <v>6706009</v>
+        <v>6705921</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132667690</v>
+        <v>132667679</v>
       </c>
       <c r="B109" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11269,21 +11269,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>411525</v>
+        <v>411585</v>
       </c>
       <c r="R109" t="n">
-        <v>6705921</v>
+        <v>6705911</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11455,7 +11455,7 @@
         <v>132667663</v>
       </c>
       <c r="B111" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>132667662</v>
       </c>
       <c r="B112" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132514331</v>
+        <v>132519427</v>
       </c>
       <c r="B9" t="n">
-        <v>81312</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,37 +1455,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411764</v>
+        <v>411777</v>
       </c>
       <c r="R9" t="n">
-        <v>6706079</v>
+        <v>6706085</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132519427</v>
+        <v>132519415</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411777</v>
+        <v>411923</v>
       </c>
       <c r="R10" t="n">
-        <v>6706085</v>
+        <v>6706141</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132519415</v>
+        <v>132514331</v>
       </c>
       <c r="B11" t="n">
-        <v>79085</v>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,37 +1649,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411923</v>
+        <v>411764</v>
       </c>
       <c r="R11" t="n">
-        <v>6706141</v>
+        <v>6706079</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,12 +1723,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132519396</v>
+        <v>132519367</v>
       </c>
       <c r="B17" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,21 +2232,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411744</v>
+        <v>411782</v>
       </c>
       <c r="R17" t="n">
-        <v>6706031</v>
+        <v>6706088</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132519403</v>
+        <v>132519396</v>
       </c>
       <c r="B18" t="n">
         <v>79085</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411785</v>
+        <v>411744</v>
       </c>
       <c r="R18" t="n">
-        <v>6706078</v>
+        <v>6706031</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132519367</v>
+        <v>132519403</v>
       </c>
       <c r="B19" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411782</v>
+        <v>411785</v>
       </c>
       <c r="R19" t="n">
-        <v>6706088</v>
+        <v>6706078</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132519435</v>
+        <v>132519390</v>
       </c>
       <c r="B28" t="n">
-        <v>78993</v>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3299,21 +3299,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>411612</v>
+        <v>411626</v>
       </c>
       <c r="R28" t="n">
-        <v>6705977</v>
+        <v>6705987</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132519390</v>
+        <v>132519435</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411626</v>
+        <v>411612</v>
       </c>
       <c r="R30" t="n">
-        <v>6705987</v>
+        <v>6705977</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3579,32 +3579,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132519394</v>
+        <v>132519376</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>79413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411741</v>
+        <v>411939</v>
       </c>
       <c r="R31" t="n">
-        <v>6706031</v>
+        <v>6706156</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132519413</v>
+        <v>132519394</v>
       </c>
       <c r="B32" t="n">
         <v>79085</v>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411921</v>
+        <v>411741</v>
       </c>
       <c r="R32" t="n">
-        <v>6706127</v>
+        <v>6706031</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3773,32 +3773,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132519376</v>
+        <v>132519413</v>
       </c>
       <c r="B33" t="n">
-        <v>79413</v>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411939</v>
+        <v>411921</v>
       </c>
       <c r="R33" t="n">
-        <v>6706156</v>
+        <v>6706127</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132519405</v>
+        <v>132514332</v>
       </c>
       <c r="B34" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,37 +3881,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411830</v>
+        <v>411910</v>
       </c>
       <c r="R34" t="n">
-        <v>6706163</v>
+        <v>6706124</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132519408</v>
+        <v>132519364</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411867</v>
+        <v>411743</v>
       </c>
       <c r="R35" t="n">
-        <v>6706121</v>
+        <v>6706033</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132519388</v>
+        <v>132514333</v>
       </c>
       <c r="B36" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,37 +4075,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411615</v>
+        <v>411597</v>
       </c>
       <c r="R36" t="n">
-        <v>6705973</v>
+        <v>6705968</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132514332</v>
+        <v>132519432</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,37 +4172,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411910</v>
+        <v>411775</v>
       </c>
       <c r="R37" t="n">
-        <v>6706124</v>
+        <v>6706079</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132519364</v>
+        <v>132519405</v>
       </c>
       <c r="B38" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411743</v>
+        <v>411830</v>
       </c>
       <c r="R38" t="n">
-        <v>6706033</v>
+        <v>6706163</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132514333</v>
+        <v>132519408</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,37 +4366,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411597</v>
+        <v>411867</v>
       </c>
       <c r="R39" t="n">
-        <v>6705968</v>
+        <v>6706121</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4440,22 +4440,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132519432</v>
+        <v>132519388</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411775</v>
+        <v>411615</v>
       </c>
       <c r="R40" t="n">
-        <v>6706079</v>
+        <v>6705973</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519411</v>
+        <v>132519374</v>
       </c>
       <c r="B41" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411909</v>
+        <v>411937</v>
       </c>
       <c r="R41" t="n">
-        <v>6706115</v>
+        <v>6706170</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519374</v>
+        <v>132519370</v>
       </c>
       <c r="B42" t="n">
         <v>79946</v>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411937</v>
+        <v>411829</v>
       </c>
       <c r="R42" t="n">
-        <v>6706170</v>
+        <v>6706165</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519370</v>
+        <v>132519411</v>
       </c>
       <c r="B43" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411829</v>
+        <v>411909</v>
       </c>
       <c r="R43" t="n">
-        <v>6706165</v>
+        <v>6706115</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132639607</v>
+        <v>132640069</v>
       </c>
       <c r="B49" t="n">
-        <v>83299</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,21 +5336,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411648</v>
+        <v>411560</v>
       </c>
       <c r="R49" t="n">
-        <v>6705948</v>
+        <v>6705975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132640069</v>
+        <v>132639955</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411560</v>
+        <v>411559</v>
       </c>
       <c r="R50" t="n">
-        <v>6705975</v>
+        <v>6705948</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132639955</v>
+        <v>132639607</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411559</v>
+        <v>411648</v>
       </c>
       <c r="R51" t="n">
         <v>6705948</v>
@@ -5907,10 +5907,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132640187</v>
+        <v>132640049</v>
       </c>
       <c r="B55" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,21 +5918,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411549</v>
+        <v>411557</v>
       </c>
       <c r="R55" t="n">
-        <v>6705962</v>
+        <v>6705961</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132640049</v>
+        <v>132640187</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411557</v>
+        <v>411549</v>
       </c>
       <c r="R56" t="n">
-        <v>6705961</v>
+        <v>6705962</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132667666</v>
+        <v>132662722</v>
       </c>
       <c r="B63" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6715,37 +6715,44 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411560</v>
+        <v>411632</v>
       </c>
       <c r="R63" t="n">
-        <v>6705963</v>
+        <v>6705947</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6777,34 +6784,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>3 olika träd</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132662722</v>
+        <v>132667666</v>
       </c>
       <c r="B64" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6812,44 +6825,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411632</v>
+        <v>411560</v>
       </c>
       <c r="R64" t="n">
-        <v>6705947</v>
+        <v>6705963</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6881,30 +6887,24 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>3 olika träd</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7202,32 +7202,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132667703</v>
+        <v>132667660</v>
       </c>
       <c r="B68" t="n">
-        <v>78993</v>
+        <v>79413</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6450</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411563</v>
+        <v>411618</v>
       </c>
       <c r="R68" t="n">
-        <v>6705954</v>
+        <v>6705941</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132667648</v>
+        <v>132667692</v>
       </c>
       <c r="B69" t="n">
-        <v>79359</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,37 +7310,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411942</v>
+        <v>411772</v>
       </c>
       <c r="R69" t="n">
-        <v>6706149</v>
+        <v>6706080</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7381,7 +7378,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7400,32 +7396,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132667660</v>
+        <v>132667703</v>
       </c>
       <c r="B70" t="n">
-        <v>79413</v>
+        <v>78993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7435,10 +7431,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411618</v>
+        <v>411563</v>
       </c>
       <c r="R70" t="n">
-        <v>6705941</v>
+        <v>6705954</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7497,10 +7493,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132667692</v>
+        <v>132667648</v>
       </c>
       <c r="B71" t="n">
-        <v>79327</v>
+        <v>79359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7508,34 +7504,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411772</v>
+        <v>411942</v>
       </c>
       <c r="R71" t="n">
-        <v>6706080</v>
+        <v>6706149</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7576,6 +7575,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132667708</v>
+        <v>132667693</v>
       </c>
       <c r="B75" t="n">
-        <v>83299</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411883</v>
+        <v>411806</v>
       </c>
       <c r="R75" t="n">
-        <v>6706128</v>
+        <v>6706080</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132667693</v>
+        <v>132667708</v>
       </c>
       <c r="B76" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>411806</v>
+        <v>411883</v>
       </c>
       <c r="R76" t="n">
-        <v>6706080</v>
+        <v>6706128</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8180,56 +8180,51 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132667029</v>
+        <v>132662723</v>
       </c>
       <c r="B78" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411607</v>
+        <v>411667</v>
       </c>
       <c r="R78" t="n">
-        <v>6705981</v>
+        <v>6705978</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8267,60 +8262,60 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132667658</v>
+        <v>132662725</v>
       </c>
       <c r="B79" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8328,13 +8323,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>411492</v>
+        <v>411718</v>
       </c>
       <c r="R79" t="n">
-        <v>6705892</v>
+        <v>6706075</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8366,79 +8361,86 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>10 olika träd</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132662725</v>
+        <v>132667029</v>
       </c>
       <c r="B80" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411718</v>
+        <v>411607</v>
       </c>
       <c r="R80" t="n">
-        <v>6706075</v>
+        <v>6705981</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8470,67 +8472,66 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>10 olika träd</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132662723</v>
+        <v>132667658</v>
       </c>
       <c r="B81" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8538,13 +8539,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>411667</v>
+        <v>411492</v>
       </c>
       <c r="R81" t="n">
-        <v>6705978</v>
+        <v>6705892</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8582,19 +8583,18 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9196,32 +9196,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132667661</v>
+        <v>132667696</v>
       </c>
       <c r="B88" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>411625</v>
+        <v>411674</v>
       </c>
       <c r="R88" t="n">
-        <v>6705944</v>
+        <v>6706071</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9293,32 +9293,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132667696</v>
+        <v>132667661</v>
       </c>
       <c r="B89" t="n">
-        <v>79327</v>
+        <v>80336</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>411674</v>
+        <v>411625</v>
       </c>
       <c r="R89" t="n">
-        <v>6706071</v>
+        <v>6705944</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9390,32 +9390,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132667688</v>
+        <v>132667655</v>
       </c>
       <c r="B90" t="n">
-        <v>80392</v>
+        <v>79946</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>411633</v>
+        <v>411610</v>
       </c>
       <c r="R90" t="n">
-        <v>6705944</v>
+        <v>6705914</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132667664</v>
+        <v>132667705</v>
       </c>
       <c r="B91" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9498,21 +9498,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>411617</v>
+        <v>411596</v>
       </c>
       <c r="R91" t="n">
-        <v>6705992</v>
+        <v>6705928</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9584,32 +9584,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132667705</v>
+        <v>132667688</v>
       </c>
       <c r="B92" t="n">
-        <v>78993</v>
+        <v>80392</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9619,10 +9619,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>411596</v>
+        <v>411633</v>
       </c>
       <c r="R92" t="n">
-        <v>6705928</v>
+        <v>6705944</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9681,10 +9681,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667655</v>
+        <v>132667664</v>
       </c>
       <c r="B93" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9692,21 +9692,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411610</v>
+        <v>411617</v>
       </c>
       <c r="R93" t="n">
-        <v>6705914</v>
+        <v>6705992</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9778,32 +9778,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132667710</v>
+        <v>132667678</v>
       </c>
       <c r="B94" t="n">
-        <v>91966</v>
+        <v>79085</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5321</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>411642</v>
+        <v>411584</v>
       </c>
       <c r="R94" t="n">
-        <v>6705943</v>
+        <v>6705909</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -9857,7 +9857,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9869,7 +9868,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -9977,10 +9976,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132667652</v>
+        <v>132662719</v>
       </c>
       <c r="B96" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9988,21 +9987,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10015,13 +10014,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>411468</v>
+        <v>411464</v>
       </c>
       <c r="R96" t="n">
-        <v>6705902</v>
+        <v>6705854</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10066,22 +10065,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132662719</v>
+        <v>132667652</v>
       </c>
       <c r="B97" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10089,21 +10088,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10116,13 +10115,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>411464</v>
+        <v>411468</v>
       </c>
       <c r="R97" t="n">
-        <v>6705854</v>
+        <v>6705902</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10167,44 +10166,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132667678</v>
+        <v>132667710</v>
       </c>
       <c r="B98" t="n">
-        <v>79085</v>
+        <v>91966</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>5321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10214,10 +10213,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>411584</v>
+        <v>411642</v>
       </c>
       <c r="R98" t="n">
-        <v>6705909</v>
+        <v>6705943</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10258,6 +10257,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10373,10 +10373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132667687</v>
+        <v>132667673</v>
       </c>
       <c r="B100" t="n">
-        <v>81312</v>
+        <v>79085</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,21 +10384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411758</v>
+        <v>411487</v>
       </c>
       <c r="R100" t="n">
-        <v>6706085</v>
+        <v>6705896</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10470,10 +10470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132667673</v>
+        <v>132667687</v>
       </c>
       <c r="B101" t="n">
-        <v>79085</v>
+        <v>81312</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10481,21 +10481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411487</v>
+        <v>411758</v>
       </c>
       <c r="R101" t="n">
-        <v>6705896</v>
+        <v>6706085</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10567,10 +10567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132667680</v>
+        <v>132667651</v>
       </c>
       <c r="B102" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10578,34 +10578,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>411869</v>
+        <v>411563</v>
       </c>
       <c r="R102" t="n">
-        <v>6706115</v>
+        <v>6705952</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10646,6 +10649,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10664,7 +10668,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132667651</v>
+        <v>132667653</v>
       </c>
       <c r="B103" t="n">
         <v>79946</v>
@@ -10702,10 +10706,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411563</v>
+        <v>411515</v>
       </c>
       <c r="R103" t="n">
-        <v>6705952</v>
+        <v>6705902</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -10963,10 +10967,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132667653</v>
+        <v>132667680</v>
       </c>
       <c r="B106" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10974,37 +10978,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411515</v>
+        <v>411869</v>
       </c>
       <c r="R106" t="n">
-        <v>6705902</v>
+        <v>6706115</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11045,7 +11046,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11064,10 +11064,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132667698</v>
+        <v>132667690</v>
       </c>
       <c r="B107" t="n">
-        <v>83173</v>
+        <v>79327</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11075,21 +11075,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411666</v>
+        <v>411525</v>
       </c>
       <c r="R107" t="n">
-        <v>6706009</v>
+        <v>6705921</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11161,10 +11161,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132667690</v>
+        <v>132667698</v>
       </c>
       <c r="B108" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411525</v>
+        <v>411666</v>
       </c>
       <c r="R108" t="n">
-        <v>6705921</v>
+        <v>6706009</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132519362</v>
+        <v>132514331</v>
       </c>
       <c r="B8" t="n">
-        <v>79946</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,37 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411626</v>
+        <v>411764</v>
       </c>
       <c r="R8" t="n">
-        <v>6705988</v>
+        <v>6706079</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132519427</v>
+        <v>132519362</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411777</v>
+        <v>411626</v>
       </c>
       <c r="R9" t="n">
-        <v>6706085</v>
+        <v>6705988</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132519415</v>
+        <v>132519427</v>
       </c>
       <c r="B10" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411923</v>
+        <v>411777</v>
       </c>
       <c r="R10" t="n">
-        <v>6706141</v>
+        <v>6706085</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132514331</v>
+        <v>132519415</v>
       </c>
       <c r="B11" t="n">
-        <v>81312</v>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,37 +1649,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411764</v>
+        <v>411923</v>
       </c>
       <c r="R11" t="n">
-        <v>6706079</v>
+        <v>6706141</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,12 +1723,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132519430</v>
+        <v>132519435</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>78993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3396,21 +3396,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411592</v>
+        <v>411612</v>
       </c>
       <c r="R29" t="n">
-        <v>6705990</v>
+        <v>6705977</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132519435</v>
+        <v>132519430</v>
       </c>
       <c r="B30" t="n">
-        <v>78993</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411612</v>
+        <v>411592</v>
       </c>
       <c r="R30" t="n">
-        <v>6705977</v>
+        <v>6705990</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519374</v>
+        <v>132519411</v>
       </c>
       <c r="B41" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411937</v>
+        <v>411909</v>
       </c>
       <c r="R41" t="n">
-        <v>6706170</v>
+        <v>6706115</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519370</v>
+        <v>132519374</v>
       </c>
       <c r="B42" t="n">
         <v>79946</v>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411829</v>
+        <v>411937</v>
       </c>
       <c r="R42" t="n">
-        <v>6706165</v>
+        <v>6706170</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519411</v>
+        <v>132519370</v>
       </c>
       <c r="B43" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411909</v>
+        <v>411829</v>
       </c>
       <c r="R43" t="n">
-        <v>6706115</v>
+        <v>6706165</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5907,10 +5907,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132640049</v>
+        <v>132640187</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,21 +5918,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411557</v>
+        <v>411549</v>
       </c>
       <c r="R55" t="n">
-        <v>6705961</v>
+        <v>6705962</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132640187</v>
+        <v>132640049</v>
       </c>
       <c r="B56" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411549</v>
+        <v>411557</v>
       </c>
       <c r="R56" t="n">
-        <v>6705962</v>
+        <v>6705961</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132662718</v>
+        <v>132667028</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6306,41 +6306,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>411446</v>
+        <v>411614</v>
       </c>
       <c r="R59" t="n">
-        <v>6705831</v>
+        <v>6705987</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6375,40 +6376,34 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>5 olika träd</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132667709</v>
+        <v>132662718</v>
       </c>
       <c r="B60" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6416,37 +6411,44 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411556</v>
+        <v>411446</v>
       </c>
       <c r="R60" t="n">
-        <v>6705948</v>
+        <v>6705831</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6478,34 +6480,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>5 olika träd</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132667028</v>
+        <v>132667709</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>78730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6513,45 +6521,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411614</v>
+        <v>411556</v>
       </c>
       <c r="R61" t="n">
-        <v>6705987</v>
+        <v>6705948</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8180,10 +8180,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132662723</v>
+        <v>132667675</v>
       </c>
       <c r="B78" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8191,40 +8191,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411667</v>
+        <v>411580</v>
       </c>
       <c r="R78" t="n">
-        <v>6705978</v>
+        <v>6705883</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8262,26 +8259,25 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132662725</v>
+        <v>132662723</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8309,11 +8305,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
@@ -8323,13 +8315,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>411718</v>
+        <v>411667</v>
       </c>
       <c r="R79" t="n">
-        <v>6706075</v>
+        <v>6705978</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8359,11 +8351,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>10 olika träd</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8391,56 +8378,55 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132667029</v>
+        <v>132662725</v>
       </c>
       <c r="B80" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411607</v>
+        <v>411718</v>
       </c>
       <c r="R80" t="n">
-        <v>6705981</v>
+        <v>6706075</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8472,31 +8458,37 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>10 olika träd</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132667658</v>
+        <v>132667029</v>
       </c>
       <c r="B81" t="n">
         <v>57141</v>
@@ -8529,23 +8521,23 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>411492</v>
+        <v>411607</v>
       </c>
       <c r="R81" t="n">
-        <v>6705892</v>
+        <v>6705981</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8589,57 +8581,65 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132667675</v>
+        <v>132667658</v>
       </c>
       <c r="B82" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>411580</v>
+        <v>411492</v>
       </c>
       <c r="R82" t="n">
-        <v>6705883</v>
+        <v>6705892</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9390,10 +9390,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132667655</v>
+        <v>132667705</v>
       </c>
       <c r="B90" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9401,21 +9401,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>411610</v>
+        <v>411596</v>
       </c>
       <c r="R90" t="n">
-        <v>6705914</v>
+        <v>6705928</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9487,32 +9487,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132667705</v>
+        <v>132667688</v>
       </c>
       <c r="B91" t="n">
-        <v>78993</v>
+        <v>80392</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>411596</v>
+        <v>411633</v>
       </c>
       <c r="R91" t="n">
-        <v>6705928</v>
+        <v>6705944</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9584,32 +9584,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132667688</v>
+        <v>132667664</v>
       </c>
       <c r="B92" t="n">
-        <v>80392</v>
+        <v>79085</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9619,10 +9619,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>411633</v>
+        <v>411617</v>
       </c>
       <c r="R92" t="n">
-        <v>6705944</v>
+        <v>6705992</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9681,10 +9681,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667664</v>
+        <v>132667655</v>
       </c>
       <c r="B93" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9692,21 +9692,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411617</v>
+        <v>411610</v>
       </c>
       <c r="R93" t="n">
-        <v>6705992</v>
+        <v>6705914</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9778,32 +9778,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132667678</v>
+        <v>132667710</v>
       </c>
       <c r="B94" t="n">
-        <v>79085</v>
+        <v>91966</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>5321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>411584</v>
+        <v>411642</v>
       </c>
       <c r="R94" t="n">
-        <v>6705909</v>
+        <v>6705943</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -9857,6 +9857,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9868,17 +9869,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132667654</v>
+        <v>132667678</v>
       </c>
       <c r="B95" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9886,37 +9887,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>411588</v>
+        <v>411584</v>
       </c>
       <c r="R95" t="n">
-        <v>6705893</v>
+        <v>6705909</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -9957,7 +9955,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9976,10 +9973,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132662719</v>
+        <v>132667654</v>
       </c>
       <c r="B96" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9987,21 +9984,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10014,13 +10011,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>411464</v>
+        <v>411588</v>
       </c>
       <c r="R96" t="n">
-        <v>6705854</v>
+        <v>6705893</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10065,22 +10062,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132667652</v>
+        <v>132662719</v>
       </c>
       <c r="B97" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10088,21 +10085,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10115,13 +10112,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>411468</v>
+        <v>411464</v>
       </c>
       <c r="R97" t="n">
-        <v>6705902</v>
+        <v>6705854</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10166,57 +10163,60 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132667710</v>
+        <v>132667652</v>
       </c>
       <c r="B98" t="n">
-        <v>91966</v>
+        <v>79946</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5321</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>411642</v>
+        <v>411468</v>
       </c>
       <c r="R98" t="n">
-        <v>6705943</v>
+        <v>6705902</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10269,17 +10269,17 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132667033</v>
+        <v>132667687</v>
       </c>
       <c r="B99" t="n">
-        <v>79327</v>
+        <v>81312</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10287,37 +10287,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411635</v>
+        <v>411758</v>
       </c>
       <c r="R99" t="n">
-        <v>6705944</v>
+        <v>6706085</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10361,12 +10361,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10470,10 +10470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132667687</v>
+        <v>132667033</v>
       </c>
       <c r="B101" t="n">
-        <v>81312</v>
+        <v>79327</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10481,37 +10481,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411758</v>
+        <v>411635</v>
       </c>
       <c r="R101" t="n">
-        <v>6706085</v>
+        <v>6705944</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10555,12 +10555,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -2221,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132519367</v>
+        <v>132519396</v>
       </c>
       <c r="B17" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,21 +2232,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411782</v>
+        <v>411744</v>
       </c>
       <c r="R17" t="n">
-        <v>6706088</v>
+        <v>6706031</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132519396</v>
+        <v>132519403</v>
       </c>
       <c r="B18" t="n">
         <v>79085</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411744</v>
+        <v>411785</v>
       </c>
       <c r="R18" t="n">
-        <v>6706031</v>
+        <v>6706078</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132519403</v>
+        <v>132519367</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411785</v>
+        <v>411782</v>
       </c>
       <c r="R19" t="n">
-        <v>6706078</v>
+        <v>6706088</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132519390</v>
+        <v>132519435</v>
       </c>
       <c r="B28" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3299,21 +3299,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>411626</v>
+        <v>411612</v>
       </c>
       <c r="R28" t="n">
-        <v>6705987</v>
+        <v>6705977</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132519435</v>
+        <v>132519430</v>
       </c>
       <c r="B29" t="n">
-        <v>78993</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3396,21 +3396,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411612</v>
+        <v>411592</v>
       </c>
       <c r="R29" t="n">
-        <v>6705977</v>
+        <v>6705990</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132519430</v>
+        <v>132519390</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411592</v>
+        <v>411626</v>
       </c>
       <c r="R30" t="n">
-        <v>6705990</v>
+        <v>6705987</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519411</v>
+        <v>132519374</v>
       </c>
       <c r="B41" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411909</v>
+        <v>411937</v>
       </c>
       <c r="R41" t="n">
-        <v>6706115</v>
+        <v>6706170</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519374</v>
+        <v>132519370</v>
       </c>
       <c r="B42" t="n">
         <v>79946</v>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411937</v>
+        <v>411829</v>
       </c>
       <c r="R42" t="n">
-        <v>6706170</v>
+        <v>6706165</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519370</v>
+        <v>132519411</v>
       </c>
       <c r="B43" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411829</v>
+        <v>411909</v>
       </c>
       <c r="R43" t="n">
-        <v>6706165</v>
+        <v>6706115</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5907,10 +5907,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132640187</v>
+        <v>132640049</v>
       </c>
       <c r="B55" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,21 +5918,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411549</v>
+        <v>411557</v>
       </c>
       <c r="R55" t="n">
-        <v>6705962</v>
+        <v>6705961</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132640049</v>
+        <v>132640187</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411557</v>
+        <v>411549</v>
       </c>
       <c r="R56" t="n">
-        <v>6705961</v>
+        <v>6705962</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132667028</v>
+        <v>132667709</v>
       </c>
       <c r="B59" t="n">
-        <v>57953</v>
+        <v>78730</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6306,45 +6306,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>411614</v>
+        <v>411556</v>
       </c>
       <c r="R59" t="n">
-        <v>6705987</v>
+        <v>6705948</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6388,12 +6380,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6510,10 +6502,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132667709</v>
+        <v>132667028</v>
       </c>
       <c r="B61" t="n">
-        <v>78730</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6521,37 +6513,45 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411556</v>
+        <v>411614</v>
       </c>
       <c r="R61" t="n">
-        <v>6705948</v>
+        <v>6705987</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7202,45 +7202,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132667660</v>
+        <v>132667648</v>
       </c>
       <c r="B68" t="n">
-        <v>79413</v>
+        <v>79359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6450</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411618</v>
+        <v>411942</v>
       </c>
       <c r="R68" t="n">
-        <v>6705941</v>
+        <v>6706149</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7281,6 +7284,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7396,32 +7400,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132667703</v>
+        <v>132667660</v>
       </c>
       <c r="B70" t="n">
-        <v>78993</v>
+        <v>79413</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6450</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7431,10 +7435,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411563</v>
+        <v>411618</v>
       </c>
       <c r="R70" t="n">
-        <v>6705954</v>
+        <v>6705941</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7493,10 +7497,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132667648</v>
+        <v>132667703</v>
       </c>
       <c r="B71" t="n">
-        <v>79359</v>
+        <v>78993</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,37 +7508,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411942</v>
+        <v>411563</v>
       </c>
       <c r="R71" t="n">
-        <v>6706149</v>
+        <v>6705954</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7575,7 +7576,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132667693</v>
+        <v>132667708</v>
       </c>
       <c r="B75" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411806</v>
+        <v>411883</v>
       </c>
       <c r="R75" t="n">
-        <v>6706080</v>
+        <v>6706128</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132667708</v>
+        <v>132667693</v>
       </c>
       <c r="B76" t="n">
-        <v>83299</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>411883</v>
+        <v>411806</v>
       </c>
       <c r="R76" t="n">
-        <v>6706128</v>
+        <v>6706080</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8180,10 +8180,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132667675</v>
+        <v>132662723</v>
       </c>
       <c r="B78" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8191,37 +8191,40 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411580</v>
+        <v>411667</v>
       </c>
       <c r="R78" t="n">
-        <v>6705883</v>
+        <v>6705978</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8259,25 +8262,26 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132662723</v>
+        <v>132662725</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8305,7 +8309,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
@@ -8315,13 +8323,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>411667</v>
+        <v>411718</v>
       </c>
       <c r="R79" t="n">
-        <v>6705978</v>
+        <v>6706075</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8351,6 +8359,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>10 olika träd</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8378,55 +8391,56 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132662725</v>
+        <v>132667029</v>
       </c>
       <c r="B80" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411718</v>
+        <v>411607</v>
       </c>
       <c r="R80" t="n">
-        <v>6706075</v>
+        <v>6705981</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8458,37 +8472,31 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>10 olika träd</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132667029</v>
+        <v>132667658</v>
       </c>
       <c r="B81" t="n">
         <v>57141</v>
@@ -8521,23 +8529,23 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>411607</v>
+        <v>411492</v>
       </c>
       <c r="R81" t="n">
-        <v>6705981</v>
+        <v>6705892</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8581,65 +8589,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132667658</v>
+        <v>132667675</v>
       </c>
       <c r="B82" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>411492</v>
+        <v>411580</v>
       </c>
       <c r="R82" t="n">
-        <v>6705892</v>
+        <v>6705883</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8698,10 +8698,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132662721</v>
+        <v>132667656</v>
       </c>
       <c r="B83" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8709,44 +8709,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>411557</v>
+        <v>411711</v>
       </c>
       <c r="R83" t="n">
-        <v>6705880</v>
+        <v>6706080</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8778,40 +8771,34 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>2 olika träd</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132667656</v>
+        <v>132662721</v>
       </c>
       <c r="B84" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8819,37 +8806,44 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>411711</v>
+        <v>411557</v>
       </c>
       <c r="R84" t="n">
-        <v>6706080</v>
+        <v>6705880</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8881,24 +8875,30 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>2 olika träd</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9002,32 +9002,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132667707</v>
+        <v>132667661</v>
       </c>
       <c r="B86" t="n">
-        <v>83299</v>
+        <v>80336</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>411675</v>
+        <v>411625</v>
       </c>
       <c r="R86" t="n">
-        <v>6705969</v>
+        <v>6705944</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9099,7 +9099,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132667694</v>
+        <v>132667696</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>411516</v>
+        <v>411674</v>
       </c>
       <c r="R87" t="n">
-        <v>6705918</v>
+        <v>6706071</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9196,10 +9196,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132667696</v>
+        <v>132667707</v>
       </c>
       <c r="B88" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9207,21 +9207,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>411674</v>
+        <v>411675</v>
       </c>
       <c r="R88" t="n">
-        <v>6706071</v>
+        <v>6705969</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9293,32 +9293,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132667661</v>
+        <v>132667694</v>
       </c>
       <c r="B89" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>411625</v>
+        <v>411516</v>
       </c>
       <c r="R89" t="n">
-        <v>6705944</v>
+        <v>6705918</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9487,32 +9487,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132667688</v>
+        <v>132667655</v>
       </c>
       <c r="B91" t="n">
-        <v>80392</v>
+        <v>79946</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>411633</v>
+        <v>411610</v>
       </c>
       <c r="R91" t="n">
-        <v>6705944</v>
+        <v>6705914</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9681,32 +9681,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667655</v>
+        <v>132667688</v>
       </c>
       <c r="B93" t="n">
-        <v>79946</v>
+        <v>80392</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411610</v>
+        <v>411633</v>
       </c>
       <c r="R93" t="n">
-        <v>6705914</v>
+        <v>6705944</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9876,10 +9876,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132667678</v>
+        <v>132662719</v>
       </c>
       <c r="B95" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9887,37 +9887,40 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>411584</v>
+        <v>411464</v>
       </c>
       <c r="R95" t="n">
-        <v>6705909</v>
+        <v>6705854</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9955,18 +9958,19 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10074,10 +10078,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132662719</v>
+        <v>132667652</v>
       </c>
       <c r="B97" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10085,21 +10089,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10112,13 +10116,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>411464</v>
+        <v>411468</v>
       </c>
       <c r="R97" t="n">
-        <v>6705854</v>
+        <v>6705902</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10163,22 +10167,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132667652</v>
+        <v>132667678</v>
       </c>
       <c r="B98" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10186,37 +10190,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>411468</v>
+        <v>411584</v>
       </c>
       <c r="R98" t="n">
-        <v>6705902</v>
+        <v>6705909</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10257,7 +10258,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132667687</v>
+        <v>132667673</v>
       </c>
       <c r="B99" t="n">
-        <v>81312</v>
+        <v>79085</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10287,21 +10287,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411758</v>
+        <v>411487</v>
       </c>
       <c r="R99" t="n">
-        <v>6706085</v>
+        <v>6705896</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10373,10 +10373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132667673</v>
+        <v>132667033</v>
       </c>
       <c r="B100" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,37 +10384,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411487</v>
+        <v>411635</v>
       </c>
       <c r="R100" t="n">
-        <v>6705896</v>
+        <v>6705944</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10458,22 +10458,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132667033</v>
+        <v>132667687</v>
       </c>
       <c r="B101" t="n">
-        <v>79327</v>
+        <v>81312</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10481,37 +10481,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411635</v>
+        <v>411758</v>
       </c>
       <c r="R101" t="n">
-        <v>6705944</v>
+        <v>6706085</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10555,22 +10555,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132667651</v>
+        <v>132667686</v>
       </c>
       <c r="B102" t="n">
-        <v>79946</v>
+        <v>81312</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10578,37 +10578,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>411563</v>
+        <v>411716</v>
       </c>
       <c r="R102" t="n">
-        <v>6705952</v>
+        <v>6706077</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10649,7 +10646,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10668,10 +10664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132667653</v>
+        <v>132667680</v>
       </c>
       <c r="B103" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10679,37 +10675,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411515</v>
+        <v>411869</v>
       </c>
       <c r="R103" t="n">
-        <v>6705902</v>
+        <v>6706115</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -10750,7 +10743,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10769,7 +10761,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132667650</v>
+        <v>132667651</v>
       </c>
       <c r="B104" t="n">
         <v>79946</v>
@@ -10807,10 +10799,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411618</v>
+        <v>411563</v>
       </c>
       <c r="R104" t="n">
-        <v>6705988</v>
+        <v>6705952</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -10870,10 +10862,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132667686</v>
+        <v>132667650</v>
       </c>
       <c r="B105" t="n">
-        <v>81312</v>
+        <v>79946</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10881,34 +10873,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>411716</v>
+        <v>411618</v>
       </c>
       <c r="R105" t="n">
-        <v>6706077</v>
+        <v>6705988</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -10949,6 +10944,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10967,10 +10963,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132667680</v>
+        <v>132667653</v>
       </c>
       <c r="B106" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10978,34 +10974,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411869</v>
+        <v>411515</v>
       </c>
       <c r="R106" t="n">
-        <v>6706115</v>
+        <v>6705902</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11046,6 +11045,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11452,7 +11452,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132667663</v>
+        <v>132667662</v>
       </c>
       <c r="B111" t="n">
         <v>91962</v>
@@ -11487,10 +11487,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411576</v>
+        <v>411595</v>
       </c>
       <c r="R111" t="n">
-        <v>6705886</v>
+        <v>6705935</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11549,7 +11549,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132667662</v>
+        <v>132667663</v>
       </c>
       <c r="B112" t="n">
         <v>91962</v>
@@ -11584,10 +11584,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411595</v>
+        <v>411576</v>
       </c>
       <c r="R112" t="n">
-        <v>6705935</v>
+        <v>6705886</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132514331</v>
+        <v>132519415</v>
       </c>
       <c r="B8" t="n">
-        <v>81312</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,37 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411764</v>
+        <v>411923</v>
       </c>
       <c r="R8" t="n">
-        <v>6706079</v>
+        <v>6706141</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132519362</v>
+        <v>132514331</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,37 +1455,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411626</v>
+        <v>411764</v>
       </c>
       <c r="R9" t="n">
-        <v>6705988</v>
+        <v>6706079</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132519427</v>
+        <v>132519362</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411777</v>
+        <v>411626</v>
       </c>
       <c r="R10" t="n">
-        <v>6706085</v>
+        <v>6705988</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132519415</v>
+        <v>132519427</v>
       </c>
       <c r="B11" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411923</v>
+        <v>411777</v>
       </c>
       <c r="R11" t="n">
-        <v>6706141</v>
+        <v>6706085</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132514332</v>
+        <v>132519405</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,37 +3881,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411910</v>
+        <v>411830</v>
       </c>
       <c r="R34" t="n">
-        <v>6706124</v>
+        <v>6706163</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132519364</v>
+        <v>132519408</v>
       </c>
       <c r="B35" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411743</v>
+        <v>411867</v>
       </c>
       <c r="R35" t="n">
-        <v>6706033</v>
+        <v>6706121</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132514333</v>
+        <v>132519388</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,37 +4075,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411597</v>
+        <v>411615</v>
       </c>
       <c r="R36" t="n">
-        <v>6705968</v>
+        <v>6705973</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132519432</v>
+        <v>132514332</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,37 +4172,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411775</v>
+        <v>411910</v>
       </c>
       <c r="R37" t="n">
-        <v>6706079</v>
+        <v>6706124</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132519405</v>
+        <v>132519364</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411830</v>
+        <v>411743</v>
       </c>
       <c r="R38" t="n">
-        <v>6706163</v>
+        <v>6706033</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132519408</v>
+        <v>132514333</v>
       </c>
       <c r="B39" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,37 +4366,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411867</v>
+        <v>411597</v>
       </c>
       <c r="R39" t="n">
-        <v>6706121</v>
+        <v>6705968</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4440,22 +4440,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132519388</v>
+        <v>132519432</v>
       </c>
       <c r="B40" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411615</v>
+        <v>411775</v>
       </c>
       <c r="R40" t="n">
-        <v>6705973</v>
+        <v>6706079</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519374</v>
+        <v>132519411</v>
       </c>
       <c r="B41" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411937</v>
+        <v>411909</v>
       </c>
       <c r="R41" t="n">
-        <v>6706170</v>
+        <v>6706115</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519370</v>
+        <v>132519374</v>
       </c>
       <c r="B42" t="n">
         <v>79946</v>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411829</v>
+        <v>411937</v>
       </c>
       <c r="R42" t="n">
-        <v>6706165</v>
+        <v>6706170</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519411</v>
+        <v>132519370</v>
       </c>
       <c r="B43" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411909</v>
+        <v>411829</v>
       </c>
       <c r="R43" t="n">
-        <v>6706115</v>
+        <v>6706165</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5713,10 +5713,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132639564</v>
+        <v>132639985</v>
       </c>
       <c r="B53" t="n">
-        <v>83299</v>
+        <v>79085</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5724,21 +5724,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>411663</v>
+        <v>411571</v>
       </c>
       <c r="R53" t="n">
-        <v>6705970</v>
+        <v>6705940</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5810,10 +5810,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132639985</v>
+        <v>132639564</v>
       </c>
       <c r="B54" t="n">
-        <v>79085</v>
+        <v>83299</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5821,21 +5821,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411571</v>
+        <v>411663</v>
       </c>
       <c r="R54" t="n">
-        <v>6705940</v>
+        <v>6705970</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5907,10 +5907,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132640049</v>
+        <v>132640187</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,21 +5918,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411557</v>
+        <v>411549</v>
       </c>
       <c r="R55" t="n">
-        <v>6705961</v>
+        <v>6705962</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132640187</v>
+        <v>132640049</v>
       </c>
       <c r="B56" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411549</v>
+        <v>411557</v>
       </c>
       <c r="R56" t="n">
-        <v>6705962</v>
+        <v>6705961</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132667708</v>
+        <v>132667665</v>
       </c>
       <c r="B75" t="n">
-        <v>83299</v>
+        <v>79085</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411883</v>
+        <v>411618</v>
       </c>
       <c r="R75" t="n">
-        <v>6706128</v>
+        <v>6705988</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132667693</v>
+        <v>132667708</v>
       </c>
       <c r="B76" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>411806</v>
+        <v>411883</v>
       </c>
       <c r="R76" t="n">
-        <v>6706080</v>
+        <v>6706128</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132667665</v>
+        <v>132667693</v>
       </c>
       <c r="B77" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8094,21 +8094,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>411618</v>
+        <v>411806</v>
       </c>
       <c r="R77" t="n">
-        <v>6705988</v>
+        <v>6706080</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8391,7 +8391,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132667029</v>
+        <v>132667658</v>
       </c>
       <c r="B80" t="n">
         <v>57141</v>
@@ -8424,23 +8424,23 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411607</v>
+        <v>411492</v>
       </c>
       <c r="R80" t="n">
-        <v>6705981</v>
+        <v>6705892</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8484,19 +8484,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132667658</v>
+        <v>132667029</v>
       </c>
       <c r="B81" t="n">
         <v>57141</v>
@@ -8529,23 +8529,23 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>411492</v>
+        <v>411607</v>
       </c>
       <c r="R81" t="n">
-        <v>6705892</v>
+        <v>6705981</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8589,12 +8589,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9002,32 +9002,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132667661</v>
+        <v>132667696</v>
       </c>
       <c r="B86" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>411625</v>
+        <v>411674</v>
       </c>
       <c r="R86" t="n">
-        <v>6705944</v>
+        <v>6706071</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132667696</v>
+        <v>132667707</v>
       </c>
       <c r="B87" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9110,21 +9110,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>411674</v>
+        <v>411675</v>
       </c>
       <c r="R87" t="n">
-        <v>6706071</v>
+        <v>6705969</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9196,10 +9196,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132667707</v>
+        <v>132667694</v>
       </c>
       <c r="B88" t="n">
-        <v>83299</v>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9207,21 +9207,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>411675</v>
+        <v>411516</v>
       </c>
       <c r="R88" t="n">
-        <v>6705969</v>
+        <v>6705918</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9293,32 +9293,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132667694</v>
+        <v>132667661</v>
       </c>
       <c r="B89" t="n">
-        <v>79327</v>
+        <v>80336</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>411516</v>
+        <v>411625</v>
       </c>
       <c r="R89" t="n">
-        <v>6705918</v>
+        <v>6705944</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9584,32 +9584,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132667664</v>
+        <v>132667688</v>
       </c>
       <c r="B92" t="n">
-        <v>79085</v>
+        <v>80392</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9619,10 +9619,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>411617</v>
+        <v>411633</v>
       </c>
       <c r="R92" t="n">
-        <v>6705992</v>
+        <v>6705944</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9681,32 +9681,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667688</v>
+        <v>132667664</v>
       </c>
       <c r="B93" t="n">
-        <v>80392</v>
+        <v>79085</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411633</v>
+        <v>411617</v>
       </c>
       <c r="R93" t="n">
-        <v>6705944</v>
+        <v>6705992</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>132519415</v>
       </c>
       <c r="B8" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>132514331</v>
       </c>
       <c r="B9" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>132519362</v>
       </c>
       <c r="B10" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>132519427</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>132519436</v>
       </c>
       <c r="B12" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>132519431</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>132519365</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132519422</v>
       </c>
       <c r="B15" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>132519433</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>132519396</v>
       </c>
       <c r="B17" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>132519403</v>
       </c>
       <c r="B18" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>132519367</v>
       </c>
       <c r="B19" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>132519428</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>132519424</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>132519372</v>
       </c>
       <c r="B22" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>132514329</v>
       </c>
       <c r="B23" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>132519400</v>
       </c>
       <c r="B24" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2997,10 +2997,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132519418</v>
+        <v>132519392</v>
       </c>
       <c r="B25" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411942</v>
+        <v>411724</v>
       </c>
       <c r="R25" t="n">
-        <v>6706165</v>
+        <v>6706039</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3094,10 +3094,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132519392</v>
+        <v>132519398</v>
       </c>
       <c r="B26" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>411724</v>
+        <v>411777</v>
       </c>
       <c r="R26" t="n">
-        <v>6706039</v>
+        <v>6706088</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3191,10 +3191,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132519398</v>
+        <v>132519418</v>
       </c>
       <c r="B27" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411777</v>
+        <v>411942</v>
       </c>
       <c r="R27" t="n">
-        <v>6706088</v>
+        <v>6706165</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>132519435</v>
       </c>
       <c r="B28" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>132519430</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>132519390</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3579,32 +3579,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132519376</v>
+        <v>132519413</v>
       </c>
       <c r="B31" t="n">
-        <v>79413</v>
+        <v>79086</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411939</v>
+        <v>411921</v>
       </c>
       <c r="R31" t="n">
-        <v>6706156</v>
+        <v>6706127</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3676,32 +3676,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132519394</v>
+        <v>132519376</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>79414</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411741</v>
+        <v>411939</v>
       </c>
       <c r="R32" t="n">
-        <v>6706031</v>
+        <v>6706156</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132519413</v>
+        <v>132519394</v>
       </c>
       <c r="B33" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411921</v>
+        <v>411741</v>
       </c>
       <c r="R33" t="n">
-        <v>6706127</v>
+        <v>6706031</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132519405</v>
+        <v>132514332</v>
       </c>
       <c r="B34" t="n">
         <v>79085</v>
@@ -3881,37 +3881,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411830</v>
+        <v>411910</v>
       </c>
       <c r="R34" t="n">
-        <v>6706163</v>
+        <v>6706124</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132519408</v>
+        <v>132519364</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411867</v>
+        <v>411743</v>
       </c>
       <c r="R35" t="n">
-        <v>6706121</v>
+        <v>6706033</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132519388</v>
+        <v>132514333</v>
       </c>
       <c r="B36" t="n">
-        <v>79085</v>
+        <v>79328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,37 +4075,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411615</v>
+        <v>411597</v>
       </c>
       <c r="R36" t="n">
-        <v>6705973</v>
+        <v>6705968</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132514332</v>
+        <v>132519432</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,37 +4172,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411910</v>
+        <v>411775</v>
       </c>
       <c r="R37" t="n">
-        <v>6706124</v>
+        <v>6706079</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132519364</v>
+        <v>132519405</v>
       </c>
       <c r="B38" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411743</v>
+        <v>411830</v>
       </c>
       <c r="R38" t="n">
-        <v>6706033</v>
+        <v>6706163</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132514333</v>
+        <v>132519388</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>79086</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,37 +4366,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411597</v>
+        <v>411615</v>
       </c>
       <c r="R39" t="n">
-        <v>6705968</v>
+        <v>6705973</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4440,22 +4440,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132519432</v>
+        <v>132519408</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>79086</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411775</v>
+        <v>411867</v>
       </c>
       <c r="R40" t="n">
-        <v>6706079</v>
+        <v>6706121</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519411</v>
+        <v>132519374</v>
       </c>
       <c r="B41" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411909</v>
+        <v>411937</v>
       </c>
       <c r="R41" t="n">
-        <v>6706115</v>
+        <v>6706170</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519374</v>
+        <v>132519370</v>
       </c>
       <c r="B42" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411937</v>
+        <v>411829</v>
       </c>
       <c r="R42" t="n">
-        <v>6706170</v>
+        <v>6706165</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519370</v>
+        <v>132519411</v>
       </c>
       <c r="B43" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411829</v>
+        <v>411909</v>
       </c>
       <c r="R43" t="n">
-        <v>6706165</v>
+        <v>6706115</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>132640387</v>
       </c>
       <c r="B44" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>132640080</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>132640284</v>
       </c>
       <c r="B46" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>132640439</v>
       </c>
       <c r="B47" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>132640452</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132640069</v>
+        <v>132639955</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411560</v>
+        <v>411559</v>
       </c>
       <c r="R49" t="n">
-        <v>6705975</v>
+        <v>6705948</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5422,10 +5422,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132639955</v>
+        <v>132640069</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411559</v>
+        <v>411560</v>
       </c>
       <c r="R50" t="n">
-        <v>6705948</v>
+        <v>6705975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5522,7 +5522,7 @@
         <v>132639607</v>
       </c>
       <c r="B51" t="n">
-        <v>83299</v>
+        <v>83300</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>132640306</v>
       </c>
       <c r="B52" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5713,10 +5713,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132639985</v>
+        <v>132639564</v>
       </c>
       <c r="B53" t="n">
-        <v>79085</v>
+        <v>83300</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5724,21 +5724,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>411571</v>
+        <v>411663</v>
       </c>
       <c r="R53" t="n">
-        <v>6705940</v>
+        <v>6705970</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5810,10 +5810,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132639564</v>
+        <v>132639985</v>
       </c>
       <c r="B54" t="n">
-        <v>83299</v>
+        <v>79086</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5821,21 +5821,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411663</v>
+        <v>411571</v>
       </c>
       <c r="R54" t="n">
-        <v>6705970</v>
+        <v>6705940</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5907,10 +5907,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132640187</v>
+        <v>132640049</v>
       </c>
       <c r="B55" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5918,21 +5918,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411549</v>
+        <v>411557</v>
       </c>
       <c r="R55" t="n">
-        <v>6705962</v>
+        <v>6705961</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132640049</v>
+        <v>132640187</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411557</v>
+        <v>411549</v>
       </c>
       <c r="R56" t="n">
-        <v>6705961</v>
+        <v>6705962</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
         <v>132641415</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>132640952</v>
       </c>
       <c r="B58" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132667709</v>
+        <v>132662718</v>
       </c>
       <c r="B59" t="n">
-        <v>78730</v>
+        <v>79328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6306,37 +6306,44 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>411556</v>
+        <v>411446</v>
       </c>
       <c r="R59" t="n">
-        <v>6705948</v>
+        <v>6705831</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6368,34 +6375,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>5 olika träd</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132662718</v>
+        <v>132667709</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>78731</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6403,44 +6416,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411446</v>
+        <v>411556</v>
       </c>
       <c r="R60" t="n">
-        <v>6705831</v>
+        <v>6705948</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6472,30 +6478,24 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>5 olika träd</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6505,7 +6505,7 @@
         <v>132667028</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>132667685</v>
       </c>
       <c r="B62" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>132662722</v>
       </c>
       <c r="B63" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>132667666</v>
       </c>
       <c r="B64" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>132667676</v>
       </c>
       <c r="B65" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7008,10 +7008,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132667684</v>
+        <v>132667674</v>
       </c>
       <c r="B66" t="n">
-        <v>81312</v>
+        <v>79086</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7019,21 +7019,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411558</v>
+        <v>411561</v>
       </c>
       <c r="R66" t="n">
-        <v>6705956</v>
+        <v>6705875</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7105,10 +7105,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132667674</v>
+        <v>132667684</v>
       </c>
       <c r="B67" t="n">
-        <v>79085</v>
+        <v>81313</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7116,21 +7116,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411561</v>
+        <v>411558</v>
       </c>
       <c r="R67" t="n">
-        <v>6705875</v>
+        <v>6705956</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7202,48 +7202,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132667648</v>
+        <v>132667660</v>
       </c>
       <c r="B68" t="n">
-        <v>79359</v>
+        <v>79414</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6450</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411942</v>
+        <v>411618</v>
       </c>
       <c r="R68" t="n">
-        <v>6706149</v>
+        <v>6705941</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7284,7 +7281,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7303,10 +7299,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132667692</v>
+        <v>132667648</v>
       </c>
       <c r="B69" t="n">
-        <v>79327</v>
+        <v>79360</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7314,34 +7310,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411772</v>
+        <v>411942</v>
       </c>
       <c r="R69" t="n">
-        <v>6706080</v>
+        <v>6706149</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7382,6 +7381,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7400,32 +7400,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132667660</v>
+        <v>132667692</v>
       </c>
       <c r="B70" t="n">
-        <v>79413</v>
+        <v>79328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411618</v>
+        <v>411772</v>
       </c>
       <c r="R70" t="n">
-        <v>6705941</v>
+        <v>6706080</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7500,7 +7500,7 @@
         <v>132667703</v>
       </c>
       <c r="B71" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>132667695</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132667649</v>
+        <v>132667691</v>
       </c>
       <c r="B73" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7702,37 +7702,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411618</v>
+        <v>411468</v>
       </c>
       <c r="R73" t="n">
-        <v>6705989</v>
+        <v>6705919</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7773,7 +7770,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7792,10 +7788,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132667691</v>
+        <v>132667649</v>
       </c>
       <c r="B74" t="n">
-        <v>79327</v>
+        <v>79947</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7803,34 +7799,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>411468</v>
+        <v>411618</v>
       </c>
       <c r="R74" t="n">
-        <v>6705919</v>
+        <v>6705989</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7871,6 +7870,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132667665</v>
+        <v>132667708</v>
       </c>
       <c r="B75" t="n">
-        <v>79085</v>
+        <v>83300</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411618</v>
+        <v>411883</v>
       </c>
       <c r="R75" t="n">
-        <v>6705988</v>
+        <v>6706128</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132667708</v>
+        <v>132667693</v>
       </c>
       <c r="B76" t="n">
-        <v>83299</v>
+        <v>79328</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>411883</v>
+        <v>411806</v>
       </c>
       <c r="R76" t="n">
-        <v>6706128</v>
+        <v>6706080</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132667693</v>
+        <v>132667665</v>
       </c>
       <c r="B77" t="n">
-        <v>79327</v>
+        <v>79086</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8094,21 +8094,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>411806</v>
+        <v>411618</v>
       </c>
       <c r="R77" t="n">
-        <v>6706080</v>
+        <v>6705988</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8180,51 +8180,56 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132662723</v>
+        <v>132667029</v>
       </c>
       <c r="B78" t="n">
-        <v>79327</v>
+        <v>57142</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411667</v>
+        <v>411607</v>
       </c>
       <c r="R78" t="n">
-        <v>6705978</v>
+        <v>6705981</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8262,60 +8267,60 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132662725</v>
+        <v>132667658</v>
       </c>
       <c r="B79" t="n">
-        <v>79327</v>
+        <v>57142</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8323,13 +8328,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>411718</v>
+        <v>411492</v>
       </c>
       <c r="R79" t="n">
-        <v>6706075</v>
+        <v>6705892</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8361,72 +8366,61 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>10 olika träd</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132667658</v>
+        <v>132662723</v>
       </c>
       <c r="B80" t="n">
-        <v>57141</v>
+        <v>79328</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8434,13 +8428,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411492</v>
+        <v>411667</v>
       </c>
       <c r="R80" t="n">
-        <v>6705892</v>
+        <v>6705978</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8478,74 +8472,74 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132667029</v>
+        <v>132662725</v>
       </c>
       <c r="B81" t="n">
-        <v>57141</v>
+        <v>79328</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>411607</v>
+        <v>411718</v>
       </c>
       <c r="R81" t="n">
-        <v>6705981</v>
+        <v>6706075</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8577,24 +8571,30 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>10 olika träd</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8604,7 +8604,7 @@
         <v>132667675</v>
       </c>
       <c r="B82" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8698,10 +8698,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132667656</v>
+        <v>132662721</v>
       </c>
       <c r="B83" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8709,37 +8709,44 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>411711</v>
+        <v>411557</v>
       </c>
       <c r="R83" t="n">
-        <v>6706080</v>
+        <v>6705880</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8771,34 +8778,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>2 olika träd</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132662721</v>
+        <v>132667656</v>
       </c>
       <c r="B84" t="n">
-        <v>79327</v>
+        <v>79947</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8806,44 +8819,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>411557</v>
+        <v>411711</v>
       </c>
       <c r="R84" t="n">
-        <v>6705880</v>
+        <v>6706080</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8875,30 +8881,24 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>2 olika träd</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8908,7 +8908,7 @@
         <v>132667672</v>
       </c>
       <c r="B85" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>132667696</v>
       </c>
       <c r="B86" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>132667707</v>
       </c>
       <c r="B87" t="n">
-        <v>83299</v>
+        <v>83300</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>132667694</v>
       </c>
       <c r="B88" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>132667661</v>
       </c>
       <c r="B89" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9390,10 +9390,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132667705</v>
+        <v>132667655</v>
       </c>
       <c r="B90" t="n">
-        <v>78993</v>
+        <v>79947</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9401,21 +9401,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>411596</v>
+        <v>411610</v>
       </c>
       <c r="R90" t="n">
-        <v>6705928</v>
+        <v>6705914</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9487,32 +9487,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132667655</v>
+        <v>132667688</v>
       </c>
       <c r="B91" t="n">
-        <v>79946</v>
+        <v>80393</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>411610</v>
+        <v>411633</v>
       </c>
       <c r="R91" t="n">
-        <v>6705914</v>
+        <v>6705944</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9584,32 +9584,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132667688</v>
+        <v>132667664</v>
       </c>
       <c r="B92" t="n">
-        <v>80392</v>
+        <v>79086</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9619,10 +9619,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>411633</v>
+        <v>411617</v>
       </c>
       <c r="R92" t="n">
-        <v>6705944</v>
+        <v>6705992</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9681,10 +9681,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667664</v>
+        <v>132667705</v>
       </c>
       <c r="B93" t="n">
-        <v>79085</v>
+        <v>78994</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9692,21 +9692,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411617</v>
+        <v>411596</v>
       </c>
       <c r="R93" t="n">
-        <v>6705992</v>
+        <v>6705928</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9781,7 +9781,7 @@
         <v>132667710</v>
       </c>
       <c r="B94" t="n">
-        <v>91966</v>
+        <v>91967</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>132662719</v>
       </c>
       <c r="B95" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>132667654</v>
       </c>
       <c r="B96" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>132667652</v>
       </c>
       <c r="B97" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>132667678</v>
       </c>
       <c r="B98" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132667673</v>
+        <v>132667033</v>
       </c>
       <c r="B99" t="n">
-        <v>79085</v>
+        <v>79328</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10287,37 +10287,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411487</v>
+        <v>411635</v>
       </c>
       <c r="R99" t="n">
-        <v>6705896</v>
+        <v>6705944</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10361,22 +10361,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132667033</v>
+        <v>132667687</v>
       </c>
       <c r="B100" t="n">
-        <v>79327</v>
+        <v>81313</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,37 +10384,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411635</v>
+        <v>411758</v>
       </c>
       <c r="R100" t="n">
-        <v>6705944</v>
+        <v>6706085</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10458,22 +10458,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132667687</v>
+        <v>132667673</v>
       </c>
       <c r="B101" t="n">
-        <v>81312</v>
+        <v>79086</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10481,21 +10481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411758</v>
+        <v>411487</v>
       </c>
       <c r="R101" t="n">
-        <v>6706085</v>
+        <v>6705896</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10570,7 +10570,7 @@
         <v>132667686</v>
       </c>
       <c r="B102" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>132667680</v>
       </c>
       <c r="B103" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>132667651</v>
       </c>
       <c r="B104" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>132667650</v>
       </c>
       <c r="B105" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>132667653</v>
       </c>
       <c r="B106" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>132667690</v>
       </c>
       <c r="B107" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>132667698</v>
       </c>
       <c r="B108" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>132667679</v>
       </c>
       <c r="B109" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>132667706</v>
       </c>
       <c r="B110" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>132667662</v>
       </c>
       <c r="B111" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>132667663</v>
       </c>
       <c r="B112" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132519415</v>
+        <v>132514331</v>
       </c>
       <c r="B8" t="n">
-        <v>79086</v>
+        <v>81313</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,37 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411923</v>
+        <v>411764</v>
       </c>
       <c r="R8" t="n">
-        <v>6706141</v>
+        <v>6706079</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132514331</v>
+        <v>132519362</v>
       </c>
       <c r="B9" t="n">
-        <v>81313</v>
+        <v>79947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,37 +1455,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411764</v>
+        <v>411626</v>
       </c>
       <c r="R9" t="n">
-        <v>6706079</v>
+        <v>6705988</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132519362</v>
+        <v>132519427</v>
       </c>
       <c r="B10" t="n">
-        <v>79947</v>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411626</v>
+        <v>411777</v>
       </c>
       <c r="R10" t="n">
-        <v>6705988</v>
+        <v>6706085</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132519427</v>
+        <v>132519415</v>
       </c>
       <c r="B11" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411777</v>
+        <v>411923</v>
       </c>
       <c r="R11" t="n">
-        <v>6706085</v>
+        <v>6706141</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132519396</v>
+        <v>132519367</v>
       </c>
       <c r="B17" t="n">
-        <v>79086</v>
+        <v>79947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,21 +2232,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411744</v>
+        <v>411782</v>
       </c>
       <c r="R17" t="n">
-        <v>6706031</v>
+        <v>6706088</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132519403</v>
+        <v>132519396</v>
       </c>
       <c r="B18" t="n">
         <v>79086</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411785</v>
+        <v>411744</v>
       </c>
       <c r="R18" t="n">
-        <v>6706078</v>
+        <v>6706031</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132519367</v>
+        <v>132519403</v>
       </c>
       <c r="B19" t="n">
-        <v>79947</v>
+        <v>79086</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411782</v>
+        <v>411785</v>
       </c>
       <c r="R19" t="n">
-        <v>6706088</v>
+        <v>6706078</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132519392</v>
+        <v>132519418</v>
       </c>
       <c r="B25" t="n">
         <v>79086</v>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411724</v>
+        <v>411942</v>
       </c>
       <c r="R25" t="n">
-        <v>6706039</v>
+        <v>6706165</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132519398</v>
+        <v>132519392</v>
       </c>
       <c r="B26" t="n">
         <v>79086</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>411777</v>
+        <v>411724</v>
       </c>
       <c r="R26" t="n">
-        <v>6706088</v>
+        <v>6706039</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3191,7 +3191,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132519418</v>
+        <v>132519398</v>
       </c>
       <c r="B27" t="n">
         <v>79086</v>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411942</v>
+        <v>411777</v>
       </c>
       <c r="R27" t="n">
-        <v>6706165</v>
+        <v>6706088</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132519413</v>
+        <v>132519394</v>
       </c>
       <c r="B31" t="n">
         <v>79086</v>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411921</v>
+        <v>411741</v>
       </c>
       <c r="R31" t="n">
-        <v>6706127</v>
+        <v>6706031</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3676,32 +3676,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132519376</v>
+        <v>132519413</v>
       </c>
       <c r="B32" t="n">
-        <v>79414</v>
+        <v>79086</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411939</v>
+        <v>411921</v>
       </c>
       <c r="R32" t="n">
-        <v>6706156</v>
+        <v>6706127</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3773,32 +3773,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132519394</v>
+        <v>132519376</v>
       </c>
       <c r="B33" t="n">
-        <v>79086</v>
+        <v>79414</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411741</v>
+        <v>411939</v>
       </c>
       <c r="R33" t="n">
-        <v>6706031</v>
+        <v>6706156</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132514332</v>
+        <v>132519405</v>
       </c>
       <c r="B34" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,37 +3881,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411910</v>
+        <v>411830</v>
       </c>
       <c r="R34" t="n">
-        <v>6706124</v>
+        <v>6706163</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132519364</v>
+        <v>132519408</v>
       </c>
       <c r="B35" t="n">
-        <v>79947</v>
+        <v>79086</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411743</v>
+        <v>411867</v>
       </c>
       <c r="R35" t="n">
-        <v>6706033</v>
+        <v>6706121</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132514333</v>
+        <v>132519388</v>
       </c>
       <c r="B36" t="n">
-        <v>79328</v>
+        <v>79086</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,37 +4075,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411597</v>
+        <v>411615</v>
       </c>
       <c r="R36" t="n">
-        <v>6705968</v>
+        <v>6705973</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132519432</v>
+        <v>132514332</v>
       </c>
       <c r="B37" t="n">
-        <v>79328</v>
+        <v>79085</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,37 +4172,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411775</v>
+        <v>411910</v>
       </c>
       <c r="R37" t="n">
-        <v>6706079</v>
+        <v>6706124</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132519405</v>
+        <v>132519364</v>
       </c>
       <c r="B38" t="n">
-        <v>79086</v>
+        <v>79947</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411830</v>
+        <v>411743</v>
       </c>
       <c r="R38" t="n">
-        <v>6706163</v>
+        <v>6706033</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132519388</v>
+        <v>132514333</v>
       </c>
       <c r="B39" t="n">
-        <v>79086</v>
+        <v>79328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,37 +4366,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411615</v>
+        <v>411597</v>
       </c>
       <c r="R39" t="n">
-        <v>6705973</v>
+        <v>6705968</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4440,22 +4440,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132519408</v>
+        <v>132519432</v>
       </c>
       <c r="B40" t="n">
-        <v>79086</v>
+        <v>79328</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411867</v>
+        <v>411775</v>
       </c>
       <c r="R40" t="n">
-        <v>6706121</v>
+        <v>6706079</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132639955</v>
+        <v>132639607</v>
       </c>
       <c r="B49" t="n">
-        <v>79328</v>
+        <v>83302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,21 +5336,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411559</v>
+        <v>411648</v>
       </c>
       <c r="R49" t="n">
         <v>6705948</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132640069</v>
+        <v>132639955</v>
       </c>
       <c r="B50" t="n">
         <v>79328</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411560</v>
+        <v>411559</v>
       </c>
       <c r="R50" t="n">
-        <v>6705975</v>
+        <v>6705948</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132639607</v>
+        <v>132640069</v>
       </c>
       <c r="B51" t="n">
-        <v>83300</v>
+        <v>79328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411648</v>
+        <v>411560</v>
       </c>
       <c r="R51" t="n">
-        <v>6705948</v>
+        <v>6705975</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5716,7 +5716,7 @@
         <v>132639564</v>
       </c>
       <c r="B53" t="n">
-        <v>83300</v>
+        <v>83302</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,10 +7008,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132667674</v>
+        <v>132667684</v>
       </c>
       <c r="B66" t="n">
-        <v>79086</v>
+        <v>81313</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7019,21 +7019,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411561</v>
+        <v>411558</v>
       </c>
       <c r="R66" t="n">
-        <v>6705875</v>
+        <v>6705956</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7105,10 +7105,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132667684</v>
+        <v>132667674</v>
       </c>
       <c r="B67" t="n">
-        <v>81313</v>
+        <v>79086</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7116,21 +7116,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411558</v>
+        <v>411561</v>
       </c>
       <c r="R67" t="n">
-        <v>6705956</v>
+        <v>6705875</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132667648</v>
+        <v>132667692</v>
       </c>
       <c r="B69" t="n">
-        <v>79360</v>
+        <v>79328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,37 +7310,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411942</v>
+        <v>411772</v>
       </c>
       <c r="R69" t="n">
-        <v>6706149</v>
+        <v>6706080</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7381,7 +7378,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7400,10 +7396,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132667692</v>
+        <v>132667703</v>
       </c>
       <c r="B70" t="n">
-        <v>79328</v>
+        <v>78994</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7411,21 +7407,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7435,10 +7431,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411772</v>
+        <v>411563</v>
       </c>
       <c r="R70" t="n">
-        <v>6706080</v>
+        <v>6705954</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7497,10 +7493,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132667703</v>
+        <v>132667648</v>
       </c>
       <c r="B71" t="n">
-        <v>78994</v>
+        <v>79360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7508,34 +7504,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411563</v>
+        <v>411942</v>
       </c>
       <c r="R71" t="n">
-        <v>6705954</v>
+        <v>6706149</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7576,6 +7575,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132667691</v>
+        <v>132667649</v>
       </c>
       <c r="B73" t="n">
-        <v>79328</v>
+        <v>79947</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7702,34 +7702,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411468</v>
+        <v>411618</v>
       </c>
       <c r="R73" t="n">
-        <v>6705919</v>
+        <v>6705989</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7770,6 +7773,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7788,10 +7792,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132667649</v>
+        <v>132667691</v>
       </c>
       <c r="B74" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7799,37 +7803,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>411618</v>
+        <v>411468</v>
       </c>
       <c r="R74" t="n">
-        <v>6705989</v>
+        <v>6705919</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7870,7 +7871,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>132667708</v>
       </c>
       <c r="B75" t="n">
-        <v>83300</v>
+        <v>83302</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8390,10 +8390,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132662723</v>
+        <v>132667675</v>
       </c>
       <c r="B80" t="n">
-        <v>79328</v>
+        <v>79086</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8401,40 +8401,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411667</v>
+        <v>411580</v>
       </c>
       <c r="R80" t="n">
-        <v>6705978</v>
+        <v>6705883</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8472,19 +8469,18 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8601,10 +8597,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132667675</v>
+        <v>132662723</v>
       </c>
       <c r="B82" t="n">
-        <v>79086</v>
+        <v>79328</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8612,37 +8608,40 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>411580</v>
+        <v>411667</v>
       </c>
       <c r="R82" t="n">
-        <v>6705883</v>
+        <v>6705978</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8680,18 +8679,19 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132667696</v>
+        <v>132667707</v>
       </c>
       <c r="B86" t="n">
-        <v>79328</v>
+        <v>83302</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9013,21 +9013,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>411674</v>
+        <v>411675</v>
       </c>
       <c r="R86" t="n">
-        <v>6706071</v>
+        <v>6705969</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132667707</v>
+        <v>132667694</v>
       </c>
       <c r="B87" t="n">
-        <v>83300</v>
+        <v>79328</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9110,21 +9110,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>411675</v>
+        <v>411516</v>
       </c>
       <c r="R87" t="n">
-        <v>6705969</v>
+        <v>6705918</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9196,32 +9196,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132667694</v>
+        <v>132667661</v>
       </c>
       <c r="B88" t="n">
-        <v>79328</v>
+        <v>80337</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>411516</v>
+        <v>411625</v>
       </c>
       <c r="R88" t="n">
-        <v>6705918</v>
+        <v>6705944</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9293,32 +9293,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132667661</v>
+        <v>132667696</v>
       </c>
       <c r="B89" t="n">
-        <v>80337</v>
+        <v>79328</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>411625</v>
+        <v>411674</v>
       </c>
       <c r="R89" t="n">
-        <v>6705944</v>
+        <v>6706071</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9390,10 +9390,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132667655</v>
+        <v>132667705</v>
       </c>
       <c r="B90" t="n">
-        <v>79947</v>
+        <v>78994</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9401,21 +9401,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>411610</v>
+        <v>411596</v>
       </c>
       <c r="R90" t="n">
-        <v>6705914</v>
+        <v>6705928</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9487,32 +9487,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132667688</v>
+        <v>132667655</v>
       </c>
       <c r="B91" t="n">
-        <v>80393</v>
+        <v>79947</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>411633</v>
+        <v>411610</v>
       </c>
       <c r="R91" t="n">
-        <v>6705944</v>
+        <v>6705914</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9681,32 +9681,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667705</v>
+        <v>132667688</v>
       </c>
       <c r="B93" t="n">
-        <v>78994</v>
+        <v>80393</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411596</v>
+        <v>411633</v>
       </c>
       <c r="R93" t="n">
-        <v>6705928</v>
+        <v>6705944</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9781,7 +9781,7 @@
         <v>132667710</v>
       </c>
       <c r="B94" t="n">
-        <v>91967</v>
+        <v>91969</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9876,10 +9876,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132662719</v>
+        <v>132667654</v>
       </c>
       <c r="B95" t="n">
-        <v>79328</v>
+        <v>79947</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9887,21 +9887,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>411464</v>
+        <v>411588</v>
       </c>
       <c r="R95" t="n">
-        <v>6705854</v>
+        <v>6705893</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9965,19 +9965,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132667654</v>
+        <v>132667652</v>
       </c>
       <c r="B96" t="n">
         <v>79947</v>
@@ -10015,10 +10015,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>411588</v>
+        <v>411468</v>
       </c>
       <c r="R96" t="n">
-        <v>6705893</v>
+        <v>6705902</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10078,10 +10078,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132667652</v>
+        <v>132662719</v>
       </c>
       <c r="B97" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10089,21 +10089,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10116,13 +10116,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>411468</v>
+        <v>411464</v>
       </c>
       <c r="R97" t="n">
-        <v>6705902</v>
+        <v>6705854</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10167,12 +10167,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132667033</v>
+        <v>132667687</v>
       </c>
       <c r="B99" t="n">
-        <v>79328</v>
+        <v>81313</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10287,37 +10287,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411635</v>
+        <v>411758</v>
       </c>
       <c r="R99" t="n">
-        <v>6705944</v>
+        <v>6706085</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10361,22 +10361,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132667687</v>
+        <v>132667033</v>
       </c>
       <c r="B100" t="n">
-        <v>81313</v>
+        <v>79328</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,37 +10384,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411758</v>
+        <v>411635</v>
       </c>
       <c r="R100" t="n">
-        <v>6706085</v>
+        <v>6705944</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10458,12 +10458,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10664,10 +10664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132667680</v>
+        <v>132667651</v>
       </c>
       <c r="B103" t="n">
-        <v>79086</v>
+        <v>79947</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10675,34 +10675,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411869</v>
+        <v>411563</v>
       </c>
       <c r="R103" t="n">
-        <v>6706115</v>
+        <v>6705952</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -10743,6 +10746,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10761,7 +10765,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132667651</v>
+        <v>132667650</v>
       </c>
       <c r="B104" t="n">
         <v>79947</v>
@@ -10799,10 +10803,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411563</v>
+        <v>411618</v>
       </c>
       <c r="R104" t="n">
-        <v>6705952</v>
+        <v>6705988</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -10862,7 +10866,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132667650</v>
+        <v>132667653</v>
       </c>
       <c r="B105" t="n">
         <v>79947</v>
@@ -10900,10 +10904,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>411618</v>
+        <v>411515</v>
       </c>
       <c r="R105" t="n">
-        <v>6705988</v>
+        <v>6705902</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -10963,10 +10967,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132667653</v>
+        <v>132667680</v>
       </c>
       <c r="B106" t="n">
-        <v>79947</v>
+        <v>79086</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10974,37 +10978,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411515</v>
+        <v>411869</v>
       </c>
       <c r="R106" t="n">
-        <v>6705902</v>
+        <v>6706115</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11045,7 +11046,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11064,10 +11064,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132667690</v>
+        <v>132667698</v>
       </c>
       <c r="B107" t="n">
-        <v>79328</v>
+        <v>83176</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11075,21 +11075,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411525</v>
+        <v>411666</v>
       </c>
       <c r="R107" t="n">
-        <v>6705921</v>
+        <v>6706009</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11161,10 +11161,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132667698</v>
+        <v>132667690</v>
       </c>
       <c r="B108" t="n">
-        <v>83174</v>
+        <v>79328</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411666</v>
+        <v>411525</v>
       </c>
       <c r="R108" t="n">
-        <v>6706009</v>
+        <v>6705921</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11452,10 +11452,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132667662</v>
+        <v>132667663</v>
       </c>
       <c r="B111" t="n">
-        <v>91963</v>
+        <v>91965</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11487,10 +11487,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411595</v>
+        <v>411576</v>
       </c>
       <c r="R111" t="n">
-        <v>6705935</v>
+        <v>6705886</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11549,10 +11549,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132667663</v>
+        <v>132667662</v>
       </c>
       <c r="B112" t="n">
-        <v>91963</v>
+        <v>91965</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11584,10 +11584,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411576</v>
+        <v>411595</v>
       </c>
       <c r="R112" t="n">
-        <v>6705886</v>
+        <v>6705935</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132514331</v>
+        <v>132519362</v>
       </c>
       <c r="B8" t="n">
-        <v>81313</v>
+        <v>79948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,37 +1358,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411764</v>
+        <v>411626</v>
       </c>
       <c r="R8" t="n">
-        <v>6706079</v>
+        <v>6705988</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132519362</v>
+        <v>132519427</v>
       </c>
       <c r="B9" t="n">
-        <v>79947</v>
+        <v>79086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411626</v>
+        <v>411777</v>
       </c>
       <c r="R9" t="n">
-        <v>6705988</v>
+        <v>6706085</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132519427</v>
+        <v>132514331</v>
       </c>
       <c r="B10" t="n">
-        <v>79085</v>
+        <v>81314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,37 +1552,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411777</v>
+        <v>411764</v>
       </c>
       <c r="R10" t="n">
-        <v>6706085</v>
+        <v>6706079</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,12 +1626,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1641,7 +1641,7 @@
         <v>132519415</v>
       </c>
       <c r="B11" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>132519436</v>
       </c>
       <c r="B12" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>132519431</v>
       </c>
       <c r="B13" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>132519365</v>
       </c>
       <c r="B14" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132519422</v>
       </c>
       <c r="B15" t="n">
-        <v>81313</v>
+        <v>81314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>132519433</v>
       </c>
       <c r="B16" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>132519367</v>
       </c>
       <c r="B17" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>132519396</v>
       </c>
       <c r="B18" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>132519403</v>
       </c>
       <c r="B19" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>132519428</v>
       </c>
       <c r="B20" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>132519424</v>
       </c>
       <c r="B21" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>132519372</v>
       </c>
       <c r="B22" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>132514329</v>
       </c>
       <c r="B23" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>132519400</v>
       </c>
       <c r="B24" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>132519418</v>
       </c>
       <c r="B25" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>132519392</v>
       </c>
       <c r="B26" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>132519398</v>
       </c>
       <c r="B27" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132519435</v>
+        <v>132519430</v>
       </c>
       <c r="B28" t="n">
-        <v>78994</v>
+        <v>79329</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3299,21 +3299,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>411612</v>
+        <v>411592</v>
       </c>
       <c r="R28" t="n">
-        <v>6705977</v>
+        <v>6705990</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132519430</v>
+        <v>132519435</v>
       </c>
       <c r="B29" t="n">
-        <v>79328</v>
+        <v>78995</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3396,21 +3396,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411592</v>
+        <v>411612</v>
       </c>
       <c r="R29" t="n">
-        <v>6705990</v>
+        <v>6705977</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3485,7 +3485,7 @@
         <v>132519390</v>
       </c>
       <c r="B30" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3579,32 +3579,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132519394</v>
+        <v>132519376</v>
       </c>
       <c r="B31" t="n">
-        <v>79086</v>
+        <v>79415</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411741</v>
+        <v>411939</v>
       </c>
       <c r="R31" t="n">
-        <v>6706031</v>
+        <v>6706156</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132519413</v>
+        <v>132519394</v>
       </c>
       <c r="B32" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411921</v>
+        <v>411741</v>
       </c>
       <c r="R32" t="n">
-        <v>6706127</v>
+        <v>6706031</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3773,32 +3773,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132519376</v>
+        <v>132519413</v>
       </c>
       <c r="B33" t="n">
-        <v>79414</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411939</v>
+        <v>411921</v>
       </c>
       <c r="R33" t="n">
-        <v>6706156</v>
+        <v>6706127</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132519405</v>
+        <v>132514332</v>
       </c>
       <c r="B34" t="n">
         <v>79086</v>
@@ -3881,37 +3881,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411830</v>
+        <v>411910</v>
       </c>
       <c r="R34" t="n">
-        <v>6706163</v>
+        <v>6706124</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132519408</v>
+        <v>132519364</v>
       </c>
       <c r="B35" t="n">
-        <v>79086</v>
+        <v>79948</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411867</v>
+        <v>411743</v>
       </c>
       <c r="R35" t="n">
-        <v>6706121</v>
+        <v>6706033</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132519388</v>
+        <v>132514333</v>
       </c>
       <c r="B36" t="n">
-        <v>79086</v>
+        <v>79329</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,37 +4075,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>H, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411615</v>
+        <v>411597</v>
       </c>
       <c r="R36" t="n">
-        <v>6705973</v>
+        <v>6705968</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4149,22 +4149,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132514332</v>
+        <v>132519432</v>
       </c>
       <c r="B37" t="n">
-        <v>79085</v>
+        <v>79329</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4172,37 +4172,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411910</v>
+        <v>411775</v>
       </c>
       <c r="R37" t="n">
-        <v>6706124</v>
+        <v>6706079</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132519364</v>
+        <v>132519405</v>
       </c>
       <c r="B38" t="n">
-        <v>79947</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411743</v>
+        <v>411830</v>
       </c>
       <c r="R38" t="n">
-        <v>6706033</v>
+        <v>6706163</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132514333</v>
+        <v>132519408</v>
       </c>
       <c r="B39" t="n">
-        <v>79328</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,37 +4366,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>H, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411597</v>
+        <v>411867</v>
       </c>
       <c r="R39" t="n">
-        <v>6705968</v>
+        <v>6706121</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4440,22 +4440,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132519432</v>
+        <v>132519388</v>
       </c>
       <c r="B40" t="n">
-        <v>79328</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411775</v>
+        <v>411615</v>
       </c>
       <c r="R40" t="n">
-        <v>6706079</v>
+        <v>6705973</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132519374</v>
+        <v>132519411</v>
       </c>
       <c r="B41" t="n">
-        <v>79947</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411937</v>
+        <v>411909</v>
       </c>
       <c r="R41" t="n">
-        <v>6706170</v>
+        <v>6706115</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132519370</v>
+        <v>132519374</v>
       </c>
       <c r="B42" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411829</v>
+        <v>411937</v>
       </c>
       <c r="R42" t="n">
-        <v>6706165</v>
+        <v>6706170</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132519411</v>
+        <v>132519370</v>
       </c>
       <c r="B43" t="n">
-        <v>79086</v>
+        <v>79948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411909</v>
+        <v>411829</v>
       </c>
       <c r="R43" t="n">
-        <v>6706115</v>
+        <v>6706165</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>132640387</v>
       </c>
       <c r="B44" t="n">
-        <v>81313</v>
+        <v>81314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>132640080</v>
       </c>
       <c r="B45" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>132640284</v>
       </c>
       <c r="B46" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>132640439</v>
       </c>
       <c r="B47" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>132640452</v>
       </c>
       <c r="B48" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>132639607</v>
       </c>
       <c r="B49" t="n">
-        <v>83302</v>
+        <v>83303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>132639955</v>
       </c>
       <c r="B50" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>132640069</v>
       </c>
       <c r="B51" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>132640306</v>
       </c>
       <c r="B52" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>132639564</v>
       </c>
       <c r="B53" t="n">
-        <v>83302</v>
+        <v>83303</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>132639985</v>
       </c>
       <c r="B54" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>132640049</v>
       </c>
       <c r="B55" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>132640187</v>
       </c>
       <c r="B56" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>132641415</v>
       </c>
       <c r="B57" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>132640952</v>
       </c>
       <c r="B58" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132662718</v>
+        <v>132667028</v>
       </c>
       <c r="B59" t="n">
-        <v>79328</v>
+        <v>57954</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6306,41 +6306,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>411446</v>
+        <v>411614</v>
       </c>
       <c r="R59" t="n">
-        <v>6705831</v>
+        <v>6705987</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6375,40 +6376,34 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>5 olika träd</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132667709</v>
+        <v>132662718</v>
       </c>
       <c r="B60" t="n">
-        <v>78731</v>
+        <v>79329</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6416,37 +6411,44 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411556</v>
+        <v>411446</v>
       </c>
       <c r="R60" t="n">
-        <v>6705948</v>
+        <v>6705831</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6478,34 +6480,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>5 olika träd</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132667028</v>
+        <v>132667709</v>
       </c>
       <c r="B61" t="n">
-        <v>57954</v>
+        <v>78732</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6513,45 +6521,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411614</v>
+        <v>411556</v>
       </c>
       <c r="R61" t="n">
-        <v>6705987</v>
+        <v>6705948</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6610,7 +6610,7 @@
         <v>132667685</v>
       </c>
       <c r="B62" t="n">
-        <v>81313</v>
+        <v>81314</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>132662722</v>
       </c>
       <c r="B63" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>132667666</v>
       </c>
       <c r="B64" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>132667676</v>
       </c>
       <c r="B65" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>132667684</v>
       </c>
       <c r="B66" t="n">
-        <v>81313</v>
+        <v>81314</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>132667674</v>
       </c>
       <c r="B67" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7202,32 +7202,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132667660</v>
+        <v>132667703</v>
       </c>
       <c r="B68" t="n">
-        <v>79414</v>
+        <v>78995</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411618</v>
+        <v>411563</v>
       </c>
       <c r="R68" t="n">
-        <v>6705941</v>
+        <v>6705954</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132667692</v>
+        <v>132667648</v>
       </c>
       <c r="B69" t="n">
-        <v>79328</v>
+        <v>79361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7310,34 +7310,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411772</v>
+        <v>411942</v>
       </c>
       <c r="R69" t="n">
-        <v>6706080</v>
+        <v>6706149</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7378,6 +7381,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7396,32 +7400,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132667703</v>
+        <v>132667660</v>
       </c>
       <c r="B70" t="n">
-        <v>78994</v>
+        <v>79415</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6450</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7431,10 +7435,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411563</v>
+        <v>411618</v>
       </c>
       <c r="R70" t="n">
-        <v>6705954</v>
+        <v>6705941</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7493,10 +7497,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132667648</v>
+        <v>132667692</v>
       </c>
       <c r="B71" t="n">
-        <v>79360</v>
+        <v>79329</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7504,37 +7508,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411942</v>
+        <v>411772</v>
       </c>
       <c r="R71" t="n">
-        <v>6706149</v>
+        <v>6706080</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7575,7 +7576,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7597,7 +7597,7 @@
         <v>132667695</v>
       </c>
       <c r="B72" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>132667649</v>
       </c>
       <c r="B73" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>132667691</v>
       </c>
       <c r="B74" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132667708</v>
+        <v>132667693</v>
       </c>
       <c r="B75" t="n">
-        <v>83302</v>
+        <v>79329</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411883</v>
+        <v>411806</v>
       </c>
       <c r="R75" t="n">
-        <v>6706128</v>
+        <v>6706080</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132667693</v>
+        <v>132667708</v>
       </c>
       <c r="B76" t="n">
-        <v>79328</v>
+        <v>83303</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>411806</v>
+        <v>411883</v>
       </c>
       <c r="R76" t="n">
-        <v>6706080</v>
+        <v>6706128</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8086,7 +8086,7 @@
         <v>132667665</v>
       </c>
       <c r="B77" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8390,10 +8390,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132667675</v>
+        <v>132662725</v>
       </c>
       <c r="B80" t="n">
-        <v>79086</v>
+        <v>79329</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8401,37 +8401,44 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>411580</v>
+        <v>411718</v>
       </c>
       <c r="R80" t="n">
-        <v>6705883</v>
+        <v>6706075</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8463,34 +8470,40 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>10 olika träd</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132662725</v>
+        <v>132662723</v>
       </c>
       <c r="B81" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8515,11 +8528,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
@@ -8529,13 +8538,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>411718</v>
+        <v>411667</v>
       </c>
       <c r="R81" t="n">
-        <v>6706075</v>
+        <v>6705978</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8565,11 +8574,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>10 olika träd</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8597,10 +8601,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132662723</v>
+        <v>132667675</v>
       </c>
       <c r="B82" t="n">
-        <v>79328</v>
+        <v>79087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8608,40 +8612,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>411667</v>
+        <v>411580</v>
       </c>
       <c r="R82" t="n">
-        <v>6705978</v>
+        <v>6705883</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8679,29 +8680,28 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132662721</v>
+        <v>132667656</v>
       </c>
       <c r="B83" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8709,44 +8709,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>411557</v>
+        <v>411711</v>
       </c>
       <c r="R83" t="n">
-        <v>6705880</v>
+        <v>6706080</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8778,40 +8771,34 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>2 olika träd</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>David Schinkler</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132667656</v>
+        <v>132662721</v>
       </c>
       <c r="B84" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8819,37 +8806,44 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>411711</v>
+        <v>411557</v>
       </c>
       <c r="R84" t="n">
-        <v>6706080</v>
+        <v>6705880</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8881,24 +8875,30 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>2 olika träd</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>David Schinkler</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>David Schinkler, Moa Björnberg Dillner, Joakim Karlsson, Jon Eklund, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8908,7 +8908,7 @@
         <v>132667672</v>
       </c>
       <c r="B85" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9002,10 +9002,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132667707</v>
+        <v>132667694</v>
       </c>
       <c r="B86" t="n">
-        <v>83302</v>
+        <v>79329</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9013,21 +9013,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>411675</v>
+        <v>411516</v>
       </c>
       <c r="R86" t="n">
-        <v>6705969</v>
+        <v>6705918</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132667694</v>
+        <v>132667707</v>
       </c>
       <c r="B87" t="n">
-        <v>79328</v>
+        <v>83303</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9110,21 +9110,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>411516</v>
+        <v>411675</v>
       </c>
       <c r="R87" t="n">
-        <v>6705918</v>
+        <v>6705969</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9196,32 +9196,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132667661</v>
+        <v>132667696</v>
       </c>
       <c r="B88" t="n">
-        <v>80337</v>
+        <v>79329</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>411625</v>
+        <v>411674</v>
       </c>
       <c r="R88" t="n">
-        <v>6705944</v>
+        <v>6706071</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9293,32 +9293,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132667696</v>
+        <v>132667661</v>
       </c>
       <c r="B89" t="n">
-        <v>79328</v>
+        <v>80338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>411674</v>
+        <v>411625</v>
       </c>
       <c r="R89" t="n">
-        <v>6706071</v>
+        <v>6705944</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9390,32 +9390,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132667705</v>
+        <v>132667688</v>
       </c>
       <c r="B90" t="n">
-        <v>78994</v>
+        <v>80394</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>411596</v>
+        <v>411633</v>
       </c>
       <c r="R90" t="n">
-        <v>6705928</v>
+        <v>6705944</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9490,7 +9490,7 @@
         <v>132667655</v>
       </c>
       <c r="B91" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132667664</v>
+        <v>132667705</v>
       </c>
       <c r="B92" t="n">
-        <v>79086</v>
+        <v>78995</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9595,21 +9595,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9619,10 +9619,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>411617</v>
+        <v>411596</v>
       </c>
       <c r="R92" t="n">
-        <v>6705992</v>
+        <v>6705928</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9681,32 +9681,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132667688</v>
+        <v>132667664</v>
       </c>
       <c r="B93" t="n">
-        <v>80393</v>
+        <v>79087</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411633</v>
+        <v>411617</v>
       </c>
       <c r="R93" t="n">
-        <v>6705944</v>
+        <v>6705992</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9778,45 +9778,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132667710</v>
+        <v>132667654</v>
       </c>
       <c r="B94" t="n">
-        <v>91969</v>
+        <v>79948</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5321</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>411642</v>
+        <v>411588</v>
       </c>
       <c r="R94" t="n">
-        <v>6705943</v>
+        <v>6705893</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -9869,17 +9872,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132667654</v>
+        <v>132667652</v>
       </c>
       <c r="B95" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9914,10 +9917,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>411588</v>
+        <v>411468</v>
       </c>
       <c r="R95" t="n">
-        <v>6705893</v>
+        <v>6705902</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -9977,48 +9980,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132667652</v>
+        <v>132667710</v>
       </c>
       <c r="B96" t="n">
-        <v>79947</v>
+        <v>91970</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>5321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>411468</v>
+        <v>411642</v>
       </c>
       <c r="R96" t="n">
-        <v>6705902</v>
+        <v>6705943</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, David Schinkler</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10081,7 +10081,7 @@
         <v>132662719</v>
       </c>
       <c r="B97" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>132667678</v>
       </c>
       <c r="B98" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132667687</v>
+        <v>132667033</v>
       </c>
       <c r="B99" t="n">
-        <v>81313</v>
+        <v>79329</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10287,37 +10287,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gästgivartjärnen, Vrm</t>
+          <t>Sörsjön Väst, Vrm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411758</v>
+        <v>411635</v>
       </c>
       <c r="R99" t="n">
-        <v>6706085</v>
+        <v>6705944</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10361,22 +10361,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132667033</v>
+        <v>132667687</v>
       </c>
       <c r="B100" t="n">
-        <v>79328</v>
+        <v>81314</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,37 +10384,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sörsjön Väst, Vrm</t>
+          <t>Gästgivartjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411635</v>
+        <v>411758</v>
       </c>
       <c r="R100" t="n">
-        <v>6705944</v>
+        <v>6706085</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10458,12 +10458,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Sebastian Kirppu, Ossian Tulin, Joakim Karlsson, David Schinkler</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10473,7 +10473,7 @@
         <v>132667673</v>
       </c>
       <c r="B101" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10567,10 +10567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132667686</v>
+        <v>132667680</v>
       </c>
       <c r="B102" t="n">
-        <v>81313</v>
+        <v>79087</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10578,21 +10578,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10602,10 +10602,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>411716</v>
+        <v>411869</v>
       </c>
       <c r="R102" t="n">
-        <v>6706077</v>
+        <v>6706115</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10667,7 +10667,7 @@
         <v>132667651</v>
       </c>
       <c r="B103" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>132667650</v>
       </c>
       <c r="B104" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>132667653</v>
       </c>
       <c r="B105" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10967,10 +10967,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132667680</v>
+        <v>132667686</v>
       </c>
       <c r="B106" t="n">
-        <v>79086</v>
+        <v>81314</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10978,21 +10978,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11002,10 +11002,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411869</v>
+        <v>411716</v>
       </c>
       <c r="R106" t="n">
-        <v>6706115</v>
+        <v>6706077</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11067,7 +11067,7 @@
         <v>132667698</v>
       </c>
       <c r="B107" t="n">
-        <v>83176</v>
+        <v>83177</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>132667690</v>
       </c>
       <c r="B108" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>132667679</v>
       </c>
       <c r="B109" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>132667706</v>
       </c>
       <c r="B110" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>132667663</v>
       </c>
       <c r="B111" t="n">
-        <v>91965</v>
+        <v>91966</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>132667662</v>
       </c>
       <c r="B112" t="n">
-        <v>91965</v>
+        <v>91966</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 18118-2026 artfynd.xlsx
+++ b/artfynd/A 18118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AZ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667648</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519437</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519438</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132639564</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132639607</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667707</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667708</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519435</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519436</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667703</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667704</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667705</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667706</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389474</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,6 +2226,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389481</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389484</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132514331</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2452,6 +2542,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519420</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2549,6 +2644,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519422</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2646,6 +2746,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640387</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2743,6 +2848,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667684</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2840,6 +2950,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667685</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2937,6 +3052,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667686</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3034,6 +3154,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667687</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3131,6 +3256,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667698</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3228,6 +3358,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519386</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3325,6 +3460,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667662</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3422,6 +3562,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667663</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3519,6 +3664,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519378</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3626,6 +3776,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132639579</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3723,6 +3878,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95989071</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3820,6 +3980,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95989076</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3917,6 +4082,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95989074</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4014,6 +4184,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95989075</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4112,6 +4287,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667710</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4209,6 +4389,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95989073</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4306,6 +4491,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95989078</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4403,6 +4593,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132514333</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4500,6 +4695,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519430</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4597,6 +4797,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519431</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4694,6 +4899,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519432</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4792,6 +5002,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519433</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4889,6 +5104,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132639955</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4986,6 +5206,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640069</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5083,6 +5308,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640080</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5180,6 +5410,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640306</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5277,6 +5512,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640439</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5374,6 +5614,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640452</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5471,6 +5716,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640523</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5568,6 +5818,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640602</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5665,6 +5920,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132641415</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5775,6 +6035,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132662718</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5876,6 +6141,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132662719</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5977,6 +6247,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132662720</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6087,6 +6362,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132662721</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6197,6 +6477,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132662722</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6298,6 +6583,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132662723</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6408,6 +6698,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132662725</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6505,6 +6800,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667033</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6602,6 +6902,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667690</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6699,6 +7004,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667691</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6796,6 +7106,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667692</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6893,6 +7208,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667693</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6990,6 +7310,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667694</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7087,6 +7412,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667695</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7184,6 +7514,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667696</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7291,6 +7626,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389490</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7388,6 +7728,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519382</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7485,6 +7830,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519385</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7582,6 +7932,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667709</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7679,6 +8034,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132514332</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7776,6 +8136,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519424</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7873,6 +8238,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519426</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7970,6 +8340,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519427</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8067,6 +8442,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519428</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8164,6 +8544,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519376</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8261,6 +8646,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667660</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8358,6 +8748,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519362</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8455,6 +8850,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519364</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8552,6 +8952,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519365</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8649,6 +9054,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519367</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8746,6 +9156,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519370</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8843,6 +9258,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519372</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8940,6 +9360,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519374</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9037,6 +9462,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640049</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9138,6 +9568,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667649</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9239,6 +9674,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667650</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9340,6 +9780,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667651</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9441,6 +9886,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667652</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9542,6 +9992,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667653</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9643,6 +10098,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667654</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9740,6 +10200,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667655</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9837,6 +10302,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667656</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9944,6 +10414,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389476</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10051,6 +10526,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389477</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10158,6 +10638,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389478</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10265,6 +10750,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389482</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10372,6 +10862,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389487</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10479,6 +10974,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389488</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10586,6 +11086,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389491</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10683,6 +11188,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667661</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10788,6 +11298,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667028</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10893,6 +11408,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667029</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10998,6 +11518,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667658</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11095,6 +11620,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95989072</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11192,6 +11722,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132514329</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11289,6 +11824,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519388</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11386,6 +11926,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519390</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11483,6 +12028,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519392</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11580,6 +12130,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519394</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11677,6 +12232,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519396</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11774,6 +12334,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519398</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11871,6 +12436,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519400</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11968,6 +12538,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519403</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12065,6 +12640,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519405</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12162,6 +12742,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519408</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12259,6 +12844,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519411</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12356,6 +12946,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519413</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12453,6 +13048,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519415</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12550,6 +13150,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132519418</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12647,6 +13252,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132639985</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12744,6 +13354,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640187</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12841,6 +13456,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640284</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12938,6 +13558,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640582</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13035,6 +13660,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132640952</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13132,6 +13762,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667664</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13229,6 +13864,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667665</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13326,6 +13966,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667666</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13423,6 +14068,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667668</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13520,6 +14170,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667671</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13617,6 +14272,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667672</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13714,6 +14374,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667673</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13811,6 +14476,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667674</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13908,6 +14578,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667675</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14005,6 +14680,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667676</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14102,6 +14782,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667678</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14199,6 +14884,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667679</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14296,6 +14986,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667680</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14393,6 +15088,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667682</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14500,6 +15200,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389475</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14607,6 +15312,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389479</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14714,6 +15424,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389480</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14821,6 +15536,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389483</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14928,6 +15648,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389486</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15035,6 +15760,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389489</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15142,6 +15872,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133389492</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15239,8 +15974,162 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667688</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>